--- a/Flujo/Input/Cobranzas/Cobranzas_2024.xlsx
+++ b/Flujo/Input/Cobranzas/Cobranzas_2024.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG41"/>
+  <dimension ref="A1:BG44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1485,7 +1485,11 @@
           <t>30/08/2024 00:00</t>
         </is>
       </c>
-      <c r="X5" s="1" t="inlineStr"/>
+      <c r="X5" s="1" t="inlineStr">
+        <is>
+          <t>03/09/2024 00:00</t>
+        </is>
+      </c>
       <c r="Y5" s="1" t="inlineStr">
         <is>
           <t>CUOTA INICIAL</t>
@@ -1518,35 +1522,59 @@
       </c>
       <c r="AE5" s="1" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>8775.00</t>
         </is>
       </c>
       <c r="AF5" s="1" t="inlineStr">
         <is>
-          <t>8775.00</t>
-        </is>
-      </c>
-      <c r="AG5" s="1" t="inlineStr"/>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AG5" s="1" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
       <c r="AH5" s="1" t="inlineStr">
         <is>
           <t>Crédito Hipotecario</t>
         </is>
       </c>
-      <c r="AI5" s="1" t="inlineStr"/>
-      <c r="AJ5" s="1" t="inlineStr"/>
-      <c r="AK5" s="1" t="inlineStr"/>
+      <c r="AI5" s="1" t="inlineStr">
+        <is>
+          <t>Scotiabank Perú</t>
+        </is>
+      </c>
+      <c r="AJ5" s="1" t="inlineStr">
+        <is>
+          <t>000-2768484</t>
+        </is>
+      </c>
+      <c r="AK5" s="1" t="inlineStr">
+        <is>
+          <t>TRANSFERENCIA BANCARIA</t>
+        </is>
+      </c>
       <c r="AL5" s="1" t="inlineStr"/>
-      <c r="AM5" s="1" t="inlineStr"/>
+      <c r="AM5" s="1" t="inlineStr">
+        <is>
+          <t>U26966</t>
+        </is>
+      </c>
       <c r="AN5" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
       <c r="AO5" s="1" t="inlineStr"/>
-      <c r="AP5" s="1" t="inlineStr"/>
+      <c r="AP5" s="1" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
       <c r="AQ5" s="1" t="inlineStr">
         <is>
-          <t>VENCIDO</t>
+          <t>CANCELADO</t>
         </is>
       </c>
       <c r="AR5" s="1" t="inlineStr"/>
@@ -1561,7 +1589,7 @@
       <c r="BA5" s="1" t="inlineStr"/>
       <c r="BB5" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="BC5" s="1" t="inlineStr">
@@ -1580,7 +1608,11 @@
           <t>000034</t>
         </is>
       </c>
-      <c r="BG5" s="1" t="inlineStr"/>
+      <c r="BG5" s="1" t="inlineStr">
+        <is>
+          <t>07/07/2026 08:47</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -1674,7 +1706,11 @@
           <t>30/09/2024 00:00</t>
         </is>
       </c>
-      <c r="X6" s="1" t="inlineStr"/>
+      <c r="X6" s="1" t="inlineStr">
+        <is>
+          <t>03/09/2024 00:00</t>
+        </is>
+      </c>
       <c r="Y6" s="1" t="inlineStr">
         <is>
           <t>CUOTA INICIAL</t>
@@ -1687,55 +1723,79 @@
       </c>
       <c r="AA6" s="1" t="inlineStr">
         <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AB6" s="1" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AC6" s="1" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AD6" s="1" t="inlineStr">
+        <is>
           <t>11775.00</t>
         </is>
       </c>
-      <c r="AB6" s="1" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="AC6" s="1" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="AD6" s="1" t="inlineStr">
-        <is>
-          <t>11775.00</t>
-        </is>
-      </c>
       <c r="AE6" s="1" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1225.00</t>
         </is>
       </c>
       <c r="AF6" s="1" t="inlineStr">
         <is>
-          <t>11775.00</t>
-        </is>
-      </c>
-      <c r="AG6" s="1" t="inlineStr"/>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AG6" s="1" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
       <c r="AH6" s="1" t="inlineStr">
         <is>
           <t>Crédito Hipotecario</t>
         </is>
       </c>
-      <c r="AI6" s="1" t="inlineStr"/>
-      <c r="AJ6" s="1" t="inlineStr"/>
-      <c r="AK6" s="1" t="inlineStr"/>
+      <c r="AI6" s="1" t="inlineStr">
+        <is>
+          <t>Scotiabank Perú</t>
+        </is>
+      </c>
+      <c r="AJ6" s="1" t="inlineStr">
+        <is>
+          <t>000-2768484</t>
+        </is>
+      </c>
+      <c r="AK6" s="1" t="inlineStr">
+        <is>
+          <t>TRANSFERENCIA BANCARIA</t>
+        </is>
+      </c>
       <c r="AL6" s="1" t="inlineStr"/>
-      <c r="AM6" s="1" t="inlineStr"/>
+      <c r="AM6" s="1" t="inlineStr">
+        <is>
+          <t>U26966</t>
+        </is>
+      </c>
       <c r="AN6" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
       <c r="AO6" s="1" t="inlineStr"/>
-      <c r="AP6" s="1" t="inlineStr"/>
+      <c r="AP6" s="1" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
       <c r="AQ6" s="1" t="inlineStr">
         <is>
-          <t>VENCIDO</t>
+          <t>CANCELADO</t>
         </is>
       </c>
       <c r="AR6" s="1" t="inlineStr"/>
@@ -1750,7 +1810,7 @@
       <c r="BA6" s="1" t="inlineStr"/>
       <c r="BB6" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="BC6" s="1" t="inlineStr">
@@ -1769,7 +1829,11 @@
           <t>000034</t>
         </is>
       </c>
-      <c r="BG6" s="1" t="inlineStr"/>
+      <c r="BG6" s="1" t="inlineStr">
+        <is>
+          <t>07/07/2026 08:47</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -1860,10 +1924,14 @@
       </c>
       <c r="W7" s="1" t="inlineStr">
         <is>
-          <t>30/12/2024 00:00</t>
-        </is>
-      </c>
-      <c r="X7" s="1" t="inlineStr"/>
+          <t>30/09/2024 00:00</t>
+        </is>
+      </c>
+      <c r="X7" s="1" t="inlineStr">
+        <is>
+          <t>04/10/2025 00:00</t>
+        </is>
+      </c>
       <c r="Y7" s="1" t="inlineStr">
         <is>
           <t>CUOTA INICIAL</t>
@@ -1871,12 +1939,12 @@
       </c>
       <c r="Z7" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA7" s="1" t="inlineStr">
         <is>
-          <t>21000.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB7" s="1" t="inlineStr">
@@ -1891,40 +1959,64 @@
       </c>
       <c r="AD7" s="1" t="inlineStr">
         <is>
-          <t>21000.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AE7" s="1" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>10000.00</t>
         </is>
       </c>
       <c r="AF7" s="1" t="inlineStr">
         <is>
-          <t>21000.00</t>
-        </is>
-      </c>
-      <c r="AG7" s="1" t="inlineStr"/>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AG7" s="1" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
       <c r="AH7" s="1" t="inlineStr">
         <is>
           <t>Crédito Hipotecario</t>
         </is>
       </c>
-      <c r="AI7" s="1" t="inlineStr"/>
-      <c r="AJ7" s="1" t="inlineStr"/>
-      <c r="AK7" s="1" t="inlineStr"/>
+      <c r="AI7" s="1" t="inlineStr">
+        <is>
+          <t>Scotiabank Perú</t>
+        </is>
+      </c>
+      <c r="AJ7" s="1" t="inlineStr">
+        <is>
+          <t>000-2768484</t>
+        </is>
+      </c>
+      <c r="AK7" s="1" t="inlineStr">
+        <is>
+          <t>TRANSFERENCIA BANCARIA</t>
+        </is>
+      </c>
       <c r="AL7" s="1" t="inlineStr"/>
-      <c r="AM7" s="1" t="inlineStr"/>
+      <c r="AM7" s="1" t="inlineStr">
+        <is>
+          <t>U27618</t>
+        </is>
+      </c>
       <c r="AN7" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
       <c r="AO7" s="1" t="inlineStr"/>
-      <c r="AP7" s="1" t="inlineStr"/>
+      <c r="AP7" s="1" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
       <c r="AQ7" s="1" t="inlineStr">
         <is>
-          <t>VENCIDO</t>
+          <t>CANCELADO</t>
         </is>
       </c>
       <c r="AR7" s="1" t="inlineStr"/>
@@ -1939,7 +2031,7 @@
       <c r="BA7" s="1" t="inlineStr"/>
       <c r="BB7" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="BC7" s="1" t="inlineStr">
@@ -1958,7 +2050,11 @@
           <t>000034</t>
         </is>
       </c>
-      <c r="BG7" s="1" t="inlineStr"/>
+      <c r="BG7" s="1" t="inlineStr">
+        <is>
+          <t>07/07/2026 08:52</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1988,17 +2084,17 @@
       </c>
       <c r="F8" s="1" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>302</t>
         </is>
       </c>
       <c r="G8" s="1" t="inlineStr">
         <is>
-          <t>490000.00</t>
+          <t>435500.00</t>
         </is>
       </c>
       <c r="H8" s="1" t="inlineStr">
         <is>
-          <t>490000.00</t>
+          <t>435500.00</t>
         </is>
       </c>
       <c r="I8" s="1" t="inlineStr"/>
@@ -2009,28 +2105,32 @@
       <c r="N8" s="1" t="inlineStr"/>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>Elizabeth Rocio Urbina Ñañez</t>
+          <t>Cristhiam Ortiz Angeles</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr">
         <is>
-          <t>71404863</t>
+          <t>45110882</t>
         </is>
       </c>
       <c r="Q8" s="1" t="inlineStr">
         <is>
-          <t>Av. Arequipa 2651</t>
-        </is>
-      </c>
-      <c r="R8" s="1" t="inlineStr"/>
+          <t>Av. Olavegoya 1879 departamento 301</t>
+        </is>
+      </c>
+      <c r="R8" s="1" t="inlineStr">
+        <is>
+          <t>992532732</t>
+        </is>
+      </c>
       <c r="S8" s="1" t="inlineStr">
         <is>
-          <t>943921218</t>
+          <t>992532732</t>
         </is>
       </c>
       <c r="T8" s="1" t="inlineStr">
         <is>
-          <t>elizabethurbina9624@gmail.com</t>
+          <t>Cristhian4520@gmail.com</t>
         </is>
       </c>
       <c r="U8" s="1" t="inlineStr">
@@ -2040,32 +2140,32 @@
       </c>
       <c r="V8" s="1" t="inlineStr">
         <is>
-          <t>LINCE</t>
+          <t>JESUS MARIA</t>
         </is>
       </c>
       <c r="W8" s="1" t="inlineStr">
         <is>
-          <t>24/11/2024 00:00</t>
+          <t>30/09/2024 00:00</t>
         </is>
       </c>
       <c r="X8" s="1" t="inlineStr">
         <is>
-          <t>24/11/2024 00:00</t>
+          <t>05/02/2025 00:00</t>
         </is>
       </c>
       <c r="Y8" s="1" t="inlineStr">
         <is>
-          <t>SEPARACION</t>
+          <t>CUOTA INICIAL</t>
         </is>
       </c>
       <c r="Z8" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA8" s="1" t="inlineStr">
         <is>
-          <t>2000.00</t>
+          <t>11775.00</t>
         </is>
       </c>
       <c r="AB8" s="1" t="inlineStr">
@@ -2080,12 +2180,12 @@
       </c>
       <c r="AD8" s="1" t="inlineStr">
         <is>
-          <t>2000.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AE8" s="1" t="inlineStr">
         <is>
-          <t>2000.00</t>
+          <t>550.00</t>
         </is>
       </c>
       <c r="AF8" s="1" t="inlineStr">
@@ -2121,7 +2221,7 @@
       <c r="AL8" s="1" t="inlineStr"/>
       <c r="AM8" s="1" t="inlineStr">
         <is>
-          <t>FD893378</t>
+          <t>U28731</t>
         </is>
       </c>
       <c r="AN8" s="1" t="inlineStr">
@@ -2157,23 +2257,23 @@
       </c>
       <c r="BC8" s="1" t="inlineStr">
         <is>
-          <t>03/04/2025 17:35</t>
+          <t>26/07/2024 14:43</t>
         </is>
       </c>
       <c r="BD8" s="1" t="inlineStr">
         <is>
-          <t>Carla Michue M</t>
+          <t>Kenny Salazar S</t>
         </is>
       </c>
       <c r="BE8" s="1" t="inlineStr"/>
       <c r="BF8" s="1" t="inlineStr">
         <is>
-          <t>000005</t>
+          <t>000034</t>
         </is>
       </c>
       <c r="BG8" s="1" t="inlineStr">
         <is>
-          <t>29/06/2026 21:44</t>
+          <t>07/07/2026 08:56</t>
         </is>
       </c>
     </row>
@@ -2205,17 +2305,17 @@
       </c>
       <c r="F9" s="1" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>302</t>
         </is>
       </c>
       <c r="G9" s="1" t="inlineStr">
         <is>
-          <t>637000.00</t>
+          <t>435500.00</t>
         </is>
       </c>
       <c r="H9" s="1" t="inlineStr">
         <is>
-          <t>637000.00</t>
+          <t>435500.00</t>
         </is>
       </c>
       <c r="I9" s="1" t="inlineStr"/>
@@ -2226,32 +2326,32 @@
       <c r="N9" s="1" t="inlineStr"/>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>Elmo Calatayud Chumbes</t>
+          <t>Cristhiam Ortiz Angeles</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr">
         <is>
-          <t>15580131</t>
+          <t>45110882</t>
         </is>
       </c>
       <c r="Q9" s="1" t="inlineStr">
         <is>
-          <t>Avenida Tomas Valles 1530 Block 14 departamento 204</t>
+          <t>Av. Olavegoya 1879 departamento 301</t>
         </is>
       </c>
       <c r="R9" s="1" t="inlineStr">
         <is>
-          <t>955600933</t>
+          <t>992532732</t>
         </is>
       </c>
       <c r="S9" s="1" t="inlineStr">
         <is>
-          <t>955600933</t>
+          <t>992532732</t>
         </is>
       </c>
       <c r="T9" s="1" t="inlineStr">
         <is>
-          <t>ec.calatayud@gmail.com</t>
+          <t>Cristhian4520@gmail.com</t>
         </is>
       </c>
       <c r="U9" s="1" t="inlineStr">
@@ -2261,32 +2361,32 @@
       </c>
       <c r="V9" s="1" t="inlineStr">
         <is>
-          <t>LOS OLIVOS</t>
+          <t>JESUS MARIA</t>
         </is>
       </c>
       <c r="W9" s="1" t="inlineStr">
         <is>
-          <t>30/10/2024 00:00</t>
+          <t>30/12/2024 00:00</t>
         </is>
       </c>
       <c r="X9" s="1" t="inlineStr">
         <is>
-          <t>30/10/2024 00:00</t>
+          <t>05/02/2025 00:00</t>
         </is>
       </c>
       <c r="Y9" s="1" t="inlineStr">
         <is>
-          <t>SEPARACION</t>
+          <t>CUOTA INICIAL</t>
         </is>
       </c>
       <c r="Z9" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="1" t="inlineStr">
         <is>
-          <t>3000.00</t>
+          <t>21000.00</t>
         </is>
       </c>
       <c r="AB9" s="1" t="inlineStr">
@@ -2301,12 +2401,12 @@
       </c>
       <c r="AD9" s="1" t="inlineStr">
         <is>
-          <t>3000.00</t>
+          <t>21000.00</t>
         </is>
       </c>
       <c r="AE9" s="1" t="inlineStr">
         <is>
-          <t>3000.00</t>
+          <t>21000.00</t>
         </is>
       </c>
       <c r="AF9" s="1" t="inlineStr">
@@ -2342,7 +2442,7 @@
       <c r="AL9" s="1" t="inlineStr"/>
       <c r="AM9" s="1" t="inlineStr">
         <is>
-          <t>04797111</t>
+          <t>U28731</t>
         </is>
       </c>
       <c r="AN9" s="1" t="inlineStr">
@@ -2378,7 +2478,7 @@
       </c>
       <c r="BC9" s="1" t="inlineStr">
         <is>
-          <t>30/11/2024 15:36</t>
+          <t>26/07/2024 14:43</t>
         </is>
       </c>
       <c r="BD9" s="1" t="inlineStr">
@@ -2389,12 +2489,12 @@
       <c r="BE9" s="1" t="inlineStr"/>
       <c r="BF9" s="1" t="inlineStr">
         <is>
-          <t>000025</t>
+          <t>000034</t>
         </is>
       </c>
       <c r="BG9" s="1" t="inlineStr">
         <is>
-          <t>26/06/2026 14:52</t>
+          <t>07/07/2026 08:56</t>
         </is>
       </c>
     </row>
@@ -2426,17 +2526,17 @@
       </c>
       <c r="F10" s="1" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>205</t>
         </is>
       </c>
       <c r="G10" s="1" t="inlineStr">
         <is>
-          <t>637000.00</t>
+          <t>490000.00</t>
         </is>
       </c>
       <c r="H10" s="1" t="inlineStr">
         <is>
-          <t>637000.00</t>
+          <t>490000.00</t>
         </is>
       </c>
       <c r="I10" s="1" t="inlineStr"/>
@@ -2447,32 +2547,28 @@
       <c r="N10" s="1" t="inlineStr"/>
       <c r="O10" s="1" t="inlineStr">
         <is>
-          <t>Elmo Calatayud Chumbes</t>
+          <t>Elizabeth Rocio Urbina Ñañez</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr">
         <is>
-          <t>15580131</t>
+          <t>71404863</t>
         </is>
       </c>
       <c r="Q10" s="1" t="inlineStr">
         <is>
-          <t>Avenida Tomas Valles 1530 Block 14 departamento 204</t>
-        </is>
-      </c>
-      <c r="R10" s="1" t="inlineStr">
-        <is>
-          <t>955600933</t>
-        </is>
-      </c>
+          <t>Av. Arequipa 2651</t>
+        </is>
+      </c>
+      <c r="R10" s="1" t="inlineStr"/>
       <c r="S10" s="1" t="inlineStr">
         <is>
-          <t>955600933</t>
+          <t>943921218</t>
         </is>
       </c>
       <c r="T10" s="1" t="inlineStr">
         <is>
-          <t>ec.calatayud@gmail.com</t>
+          <t>elizabethurbina9624@gmail.com</t>
         </is>
       </c>
       <c r="U10" s="1" t="inlineStr">
@@ -2482,22 +2578,22 @@
       </c>
       <c r="V10" s="1" t="inlineStr">
         <is>
-          <t>LOS OLIVOS</t>
+          <t>LINCE</t>
         </is>
       </c>
       <c r="W10" s="1" t="inlineStr">
         <is>
-          <t>30/11/2024 00:00</t>
+          <t>24/11/2024 00:00</t>
         </is>
       </c>
       <c r="X10" s="1" t="inlineStr">
         <is>
-          <t>30/11/2024 00:00</t>
+          <t>24/11/2024 00:00</t>
         </is>
       </c>
       <c r="Y10" s="1" t="inlineStr">
         <is>
-          <t>CUOTA INICIAL</t>
+          <t>SEPARACION</t>
         </is>
       </c>
       <c r="Z10" s="1" t="inlineStr">
@@ -2507,7 +2603,7 @@
       </c>
       <c r="AA10" s="1" t="inlineStr">
         <is>
-          <t>27000.00</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="AB10" s="1" t="inlineStr">
@@ -2522,12 +2618,12 @@
       </c>
       <c r="AD10" s="1" t="inlineStr">
         <is>
-          <t>27000.00</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="AE10" s="1" t="inlineStr">
         <is>
-          <t>27000.00</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="AF10" s="1" t="inlineStr">
@@ -2563,7 +2659,7 @@
       <c r="AL10" s="1" t="inlineStr"/>
       <c r="AM10" s="1" t="inlineStr">
         <is>
-          <t>78446555266223</t>
+          <t>FD893378</t>
         </is>
       </c>
       <c r="AN10" s="1" t="inlineStr">
@@ -2599,23 +2695,23 @@
       </c>
       <c r="BC10" s="1" t="inlineStr">
         <is>
-          <t>30/11/2024 15:36</t>
+          <t>03/04/2025 17:35</t>
         </is>
       </c>
       <c r="BD10" s="1" t="inlineStr">
         <is>
-          <t>Kenny Salazar S</t>
+          <t>Carla Michue M</t>
         </is>
       </c>
       <c r="BE10" s="1" t="inlineStr"/>
       <c r="BF10" s="1" t="inlineStr">
         <is>
-          <t>000025</t>
+          <t>000005</t>
         </is>
       </c>
       <c r="BG10" s="1" t="inlineStr">
         <is>
-          <t>26/06/2026 14:53</t>
+          <t>29/06/2026 21:44</t>
         </is>
       </c>
     </row>
@@ -2708,22 +2804,22 @@
       </c>
       <c r="W11" s="1" t="inlineStr">
         <is>
-          <t>30/11/2024 00:00</t>
+          <t>30/10/2024 00:00</t>
         </is>
       </c>
       <c r="X11" s="1" t="inlineStr">
         <is>
-          <t>30/11/2024 00:00</t>
+          <t>30/10/2024 00:00</t>
         </is>
       </c>
       <c r="Y11" s="1" t="inlineStr">
         <is>
-          <t>CUOTA INICIAL</t>
+          <t>SEPARACION</t>
         </is>
       </c>
       <c r="Z11" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA11" s="1" t="inlineStr">
@@ -2784,7 +2880,7 @@
       <c r="AL11" s="1" t="inlineStr"/>
       <c r="AM11" s="1" t="inlineStr">
         <is>
-          <t>7844655544194</t>
+          <t>04797111</t>
         </is>
       </c>
       <c r="AN11" s="1" t="inlineStr">
@@ -2836,7 +2932,7 @@
       </c>
       <c r="BG11" s="1" t="inlineStr">
         <is>
-          <t>26/06/2026 14:53</t>
+          <t>26/06/2026 14:52</t>
         </is>
       </c>
     </row>
@@ -2929,12 +3025,12 @@
       </c>
       <c r="W12" s="1" t="inlineStr">
         <is>
-          <t>30/12/2024 00:00</t>
+          <t>30/11/2024 00:00</t>
         </is>
       </c>
       <c r="X12" s="1" t="inlineStr">
         <is>
-          <t>30/12/2024 00:00</t>
+          <t>30/11/2024 00:00</t>
         </is>
       </c>
       <c r="Y12" s="1" t="inlineStr">
@@ -2944,12 +3040,12 @@
       </c>
       <c r="Z12" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA12" s="1" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>27000.00</t>
         </is>
       </c>
       <c r="AB12" s="1" t="inlineStr">
@@ -2964,12 +3060,12 @@
       </c>
       <c r="AD12" s="1" t="inlineStr">
         <is>
-          <t>30700.00</t>
+          <t>27000.00</t>
         </is>
       </c>
       <c r="AE12" s="1" t="inlineStr">
         <is>
-          <t>30000.00</t>
+          <t>27000.00</t>
         </is>
       </c>
       <c r="AF12" s="1" t="inlineStr">
@@ -3005,7 +3101,7 @@
       <c r="AL12" s="1" t="inlineStr"/>
       <c r="AM12" s="1" t="inlineStr">
         <is>
-          <t>7844655610530</t>
+          <t>78446555266223</t>
         </is>
       </c>
       <c r="AN12" s="1" t="inlineStr">
@@ -3057,7 +3153,7 @@
       </c>
       <c r="BG12" s="1" t="inlineStr">
         <is>
-          <t>26/06/2026 14:55</t>
+          <t>26/06/2026 14:53</t>
         </is>
       </c>
     </row>
@@ -3150,12 +3246,12 @@
       </c>
       <c r="W13" s="1" t="inlineStr">
         <is>
-          <t>30/12/2024 00:00</t>
+          <t>30/11/2024 00:00</t>
         </is>
       </c>
       <c r="X13" s="1" t="inlineStr">
         <is>
-          <t>30/12/2024 00:00</t>
+          <t>30/11/2024 00:00</t>
         </is>
       </c>
       <c r="Y13" s="1" t="inlineStr">
@@ -3165,12 +3261,12 @@
       </c>
       <c r="Z13" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA13" s="1" t="inlineStr">
         <is>
-          <t>30700.00</t>
+          <t>3000.00</t>
         </is>
       </c>
       <c r="AB13" s="1" t="inlineStr">
@@ -3185,12 +3281,12 @@
       </c>
       <c r="AD13" s="1" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3000.00</t>
         </is>
       </c>
       <c r="AE13" s="1" t="inlineStr">
         <is>
-          <t>700.00</t>
+          <t>3000.00</t>
         </is>
       </c>
       <c r="AF13" s="1" t="inlineStr">
@@ -3226,7 +3322,7 @@
       <c r="AL13" s="1" t="inlineStr"/>
       <c r="AM13" s="1" t="inlineStr">
         <is>
-          <t>7844655610860</t>
+          <t>7844655544194</t>
         </is>
       </c>
       <c r="AN13" s="1" t="inlineStr">
@@ -3278,7 +3374,7 @@
       </c>
       <c r="BG13" s="1" t="inlineStr">
         <is>
-          <t>26/06/2026 14:56</t>
+          <t>26/06/2026 14:53</t>
         </is>
       </c>
     </row>
@@ -3310,73 +3406,53 @@
       </c>
       <c r="F14" s="1" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G14" s="1" t="inlineStr">
         <is>
-          <t>654000.00</t>
+          <t>637000.00</t>
         </is>
       </c>
       <c r="H14" s="1" t="inlineStr">
         <is>
-          <t>654000.00</t>
-        </is>
-      </c>
-      <c r="I14" s="1" t="inlineStr">
-        <is>
-          <t>Edificio</t>
-        </is>
-      </c>
-      <c r="J14" s="1" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K14" s="1" t="inlineStr">
-        <is>
-          <t>Estacionamiento</t>
-        </is>
-      </c>
-      <c r="L14" s="1" t="inlineStr">
-        <is>
-          <t>E 12 - D 09</t>
-        </is>
-      </c>
-      <c r="M14" s="1" t="inlineStr">
-        <is>
-          <t>56300.00</t>
-        </is>
-      </c>
-      <c r="N14" s="1" t="inlineStr">
-        <is>
-          <t>56300.00</t>
-        </is>
-      </c>
+          <t>637000.00</t>
+        </is>
+      </c>
+      <c r="I14" s="1" t="inlineStr"/>
+      <c r="J14" s="1" t="inlineStr"/>
+      <c r="K14" s="1" t="inlineStr"/>
+      <c r="L14" s="1" t="inlineStr"/>
+      <c r="M14" s="1" t="inlineStr"/>
+      <c r="N14" s="1" t="inlineStr"/>
       <c r="O14" s="1" t="inlineStr">
         <is>
-          <t>Gilberto Videla Flores</t>
+          <t>Elmo Calatayud Chumbes</t>
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr">
         <is>
-          <t>06571347</t>
+          <t>15580131</t>
         </is>
       </c>
       <c r="Q14" s="1" t="inlineStr">
         <is>
-          <t>Mz D Lt 7 Urb. La Estrella</t>
-        </is>
-      </c>
-      <c r="R14" s="1" t="inlineStr"/>
+          <t>Avenida Tomas Valles 1530 Block 14 departamento 204</t>
+        </is>
+      </c>
+      <c r="R14" s="1" t="inlineStr">
+        <is>
+          <t>955600933</t>
+        </is>
+      </c>
       <c r="S14" s="1" t="inlineStr">
         <is>
-          <t>969742622</t>
+          <t>955600933</t>
         </is>
       </c>
       <c r="T14" s="1" t="inlineStr">
         <is>
-          <t>gvidelaf@gmail.com</t>
+          <t>ec.calatayud@gmail.com</t>
         </is>
       </c>
       <c r="U14" s="1" t="inlineStr">
@@ -3391,27 +3467,27 @@
       </c>
       <c r="W14" s="1" t="inlineStr">
         <is>
-          <t>31/08/2024 00:00</t>
+          <t>30/12/2024 00:00</t>
         </is>
       </c>
       <c r="X14" s="1" t="inlineStr">
         <is>
-          <t>31/08/2024 00:00</t>
+          <t>30/12/2024 00:00</t>
         </is>
       </c>
       <c r="Y14" s="1" t="inlineStr">
         <is>
-          <t>SEPARACION</t>
+          <t>CUOTA INICIAL</t>
         </is>
       </c>
       <c r="Z14" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA14" s="1" t="inlineStr">
         <is>
-          <t>3000.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB14" s="1" t="inlineStr">
@@ -3426,12 +3502,12 @@
       </c>
       <c r="AD14" s="1" t="inlineStr">
         <is>
-          <t>3000.00</t>
+          <t>30700.00</t>
         </is>
       </c>
       <c r="AE14" s="1" t="inlineStr">
         <is>
-          <t>3000.00</t>
+          <t>30000.00</t>
         </is>
       </c>
       <c r="AF14" s="1" t="inlineStr">
@@ -3446,7 +3522,7 @@
       </c>
       <c r="AH14" s="1" t="inlineStr">
         <is>
-          <t>Crédito Directo</t>
+          <t>Crédito Hipotecario</t>
         </is>
       </c>
       <c r="AI14" s="1" t="inlineStr">
@@ -3461,17 +3537,13 @@
       </c>
       <c r="AK14" s="1" t="inlineStr">
         <is>
-          <t>POS VISA</t>
-        </is>
-      </c>
-      <c r="AL14" s="1" t="inlineStr">
-        <is>
-          <t>06571347</t>
-        </is>
-      </c>
+          <t>TRANSFERENCIA BANCARIA</t>
+        </is>
+      </c>
+      <c r="AL14" s="1" t="inlineStr"/>
       <c r="AM14" s="1" t="inlineStr">
         <is>
-          <t>0059</t>
+          <t>7844655610530</t>
         </is>
       </c>
       <c r="AN14" s="1" t="inlineStr">
@@ -3479,14 +3551,10 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AO14" s="1" t="inlineStr">
-        <is>
-          <t>NO PRECISA</t>
-        </is>
-      </c>
+      <c r="AO14" s="1" t="inlineStr"/>
       <c r="AP14" s="1" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="AQ14" s="1" t="inlineStr">
@@ -3511,23 +3579,23 @@
       </c>
       <c r="BC14" s="1" t="inlineStr">
         <is>
-          <t>31/08/2024 00:00</t>
+          <t>30/11/2024 15:36</t>
         </is>
       </c>
       <c r="BD14" s="1" t="inlineStr">
         <is>
-          <t>Carla Michue M</t>
+          <t>Kenny Salazar S</t>
         </is>
       </c>
       <c r="BE14" s="1" t="inlineStr"/>
       <c r="BF14" s="1" t="inlineStr">
         <is>
-          <t>000024</t>
+          <t>000025</t>
         </is>
       </c>
       <c r="BG14" s="1" t="inlineStr">
         <is>
-          <t>29/05/2026 12:21</t>
+          <t>26/06/2026 14:55</t>
         </is>
       </c>
     </row>
@@ -3559,73 +3627,53 @@
       </c>
       <c r="F15" s="1" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G15" s="1" t="inlineStr">
         <is>
-          <t>654000.00</t>
+          <t>637000.00</t>
         </is>
       </c>
       <c r="H15" s="1" t="inlineStr">
         <is>
-          <t>654000.00</t>
-        </is>
-      </c>
-      <c r="I15" s="1" t="inlineStr">
-        <is>
-          <t>Edificio</t>
-        </is>
-      </c>
-      <c r="J15" s="1" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K15" s="1" t="inlineStr">
-        <is>
-          <t>Estacionamiento</t>
-        </is>
-      </c>
-      <c r="L15" s="1" t="inlineStr">
-        <is>
-          <t>E 12 - D 09</t>
-        </is>
-      </c>
-      <c r="M15" s="1" t="inlineStr">
-        <is>
-          <t>56300.00</t>
-        </is>
-      </c>
-      <c r="N15" s="1" t="inlineStr">
-        <is>
-          <t>56300.00</t>
-        </is>
-      </c>
+          <t>637000.00</t>
+        </is>
+      </c>
+      <c r="I15" s="1" t="inlineStr"/>
+      <c r="J15" s="1" t="inlineStr"/>
+      <c r="K15" s="1" t="inlineStr"/>
+      <c r="L15" s="1" t="inlineStr"/>
+      <c r="M15" s="1" t="inlineStr"/>
+      <c r="N15" s="1" t="inlineStr"/>
       <c r="O15" s="1" t="inlineStr">
         <is>
-          <t>Gilberto Videla Flores</t>
+          <t>Elmo Calatayud Chumbes</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr">
         <is>
-          <t>06571347</t>
+          <t>15580131</t>
         </is>
       </c>
       <c r="Q15" s="1" t="inlineStr">
         <is>
-          <t>Mz D Lt 7 Urb. La Estrella</t>
-        </is>
-      </c>
-      <c r="R15" s="1" t="inlineStr"/>
+          <t>Avenida Tomas Valles 1530 Block 14 departamento 204</t>
+        </is>
+      </c>
+      <c r="R15" s="1" t="inlineStr">
+        <is>
+          <t>955600933</t>
+        </is>
+      </c>
       <c r="S15" s="1" t="inlineStr">
         <is>
-          <t>969742622</t>
+          <t>955600933</t>
         </is>
       </c>
       <c r="T15" s="1" t="inlineStr">
         <is>
-          <t>gvidelaf@gmail.com</t>
+          <t>ec.calatayud@gmail.com</t>
         </is>
       </c>
       <c r="U15" s="1" t="inlineStr">
@@ -3640,12 +3688,12 @@
       </c>
       <c r="W15" s="1" t="inlineStr">
         <is>
-          <t>04/09/2024 00:00</t>
+          <t>30/12/2024 00:00</t>
         </is>
       </c>
       <c r="X15" s="1" t="inlineStr">
         <is>
-          <t>04/09/2024 00:00</t>
+          <t>30/12/2024 00:00</t>
         </is>
       </c>
       <c r="Y15" s="1" t="inlineStr">
@@ -3655,12 +3703,12 @@
       </c>
       <c r="Z15" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA15" s="1" t="inlineStr">
         <is>
-          <t>281120.00</t>
+          <t>30700.00</t>
         </is>
       </c>
       <c r="AB15" s="1" t="inlineStr">
@@ -3675,12 +3723,12 @@
       </c>
       <c r="AD15" s="1" t="inlineStr">
         <is>
-          <t>281120.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AE15" s="1" t="inlineStr">
         <is>
-          <t>281120.00</t>
+          <t>700.00</t>
         </is>
       </c>
       <c r="AF15" s="1" t="inlineStr">
@@ -3695,7 +3743,7 @@
       </c>
       <c r="AH15" s="1" t="inlineStr">
         <is>
-          <t>Crédito Directo</t>
+          <t>Crédito Hipotecario</t>
         </is>
       </c>
       <c r="AI15" s="1" t="inlineStr">
@@ -3716,7 +3764,7 @@
       <c r="AL15" s="1" t="inlineStr"/>
       <c r="AM15" s="1" t="inlineStr">
         <is>
-          <t>0953413</t>
+          <t>7844655610860</t>
         </is>
       </c>
       <c r="AN15" s="1" t="inlineStr">
@@ -3752,23 +3800,23 @@
       </c>
       <c r="BC15" s="1" t="inlineStr">
         <is>
-          <t>31/08/2024 00:00</t>
+          <t>30/11/2024 15:36</t>
         </is>
       </c>
       <c r="BD15" s="1" t="inlineStr">
         <is>
-          <t>Carla Michue M</t>
+          <t>Kenny Salazar S</t>
         </is>
       </c>
       <c r="BE15" s="1" t="inlineStr"/>
       <c r="BF15" s="1" t="inlineStr">
         <is>
-          <t>000024</t>
+          <t>000025</t>
         </is>
       </c>
       <c r="BG15" s="1" t="inlineStr">
         <is>
-          <t>30/06/2026 16:33</t>
+          <t>26/06/2026 14:56</t>
         </is>
       </c>
     </row>
@@ -3881,27 +3929,27 @@
       </c>
       <c r="W16" s="1" t="inlineStr">
         <is>
-          <t>30/09/2024 00:00</t>
+          <t>31/08/2024 00:00</t>
         </is>
       </c>
       <c r="X16" s="1" t="inlineStr">
         <is>
-          <t>24/09/2024 00:00</t>
+          <t>31/08/2024 00:00</t>
         </is>
       </c>
       <c r="Y16" s="1" t="inlineStr">
         <is>
-          <t>SALDO FINANCIAR</t>
+          <t>SEPARACION</t>
         </is>
       </c>
       <c r="Z16" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA16" s="1" t="inlineStr">
         <is>
-          <t>248605.00</t>
+          <t>3000.00</t>
         </is>
       </c>
       <c r="AB16" s="1" t="inlineStr">
@@ -3916,12 +3964,12 @@
       </c>
       <c r="AD16" s="1" t="inlineStr">
         <is>
-          <t>248605.00</t>
+          <t>3000.00</t>
         </is>
       </c>
       <c r="AE16" s="1" t="inlineStr">
         <is>
-          <t>248605.00</t>
+          <t>3000.00</t>
         </is>
       </c>
       <c r="AF16" s="1" t="inlineStr">
@@ -3951,13 +3999,17 @@
       </c>
       <c r="AK16" s="1" t="inlineStr">
         <is>
-          <t>TRANSFERENCIA BANCARIA</t>
-        </is>
-      </c>
-      <c r="AL16" s="1" t="inlineStr"/>
+          <t>POS VISA</t>
+        </is>
+      </c>
+      <c r="AL16" s="1" t="inlineStr">
+        <is>
+          <t>06571347</t>
+        </is>
+      </c>
       <c r="AM16" s="1" t="inlineStr">
         <is>
-          <t>0036913</t>
+          <t>0059</t>
         </is>
       </c>
       <c r="AN16" s="1" t="inlineStr">
@@ -3965,10 +4017,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AO16" s="1" t="inlineStr"/>
+      <c r="AO16" s="1" t="inlineStr">
+        <is>
+          <t>NO PRECISA</t>
+        </is>
+      </c>
       <c r="AP16" s="1" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AQ16" s="1" t="inlineStr">
@@ -4009,7 +4065,7 @@
       </c>
       <c r="BG16" s="1" t="inlineStr">
         <is>
-          <t>30/06/2026 16:48</t>
+          <t>29/05/2026 12:21</t>
         </is>
       </c>
     </row>
@@ -4041,17 +4097,17 @@
       </c>
       <c r="F17" s="1" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>203</t>
         </is>
       </c>
       <c r="G17" s="1" t="inlineStr">
         <is>
-          <t>609100.00</t>
+          <t>654000.00</t>
         </is>
       </c>
       <c r="H17" s="1" t="inlineStr">
         <is>
-          <t>609100.00</t>
+          <t>654000.00</t>
         </is>
       </c>
       <c r="I17" s="1" t="inlineStr">
@@ -4071,47 +4127,43 @@
       </c>
       <c r="L17" s="1" t="inlineStr">
         <is>
-          <t>E 26 - D 20</t>
+          <t>E 12 - D 09</t>
         </is>
       </c>
       <c r="M17" s="1" t="inlineStr">
         <is>
-          <t>64600.00</t>
+          <t>56300.00</t>
         </is>
       </c>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>64600.00</t>
+          <t>56300.00</t>
         </is>
       </c>
       <c r="O17" s="1" t="inlineStr">
         <is>
-          <t>Gilda Victoria Sampi González</t>
+          <t>Gilberto Videla Flores</t>
         </is>
       </c>
       <c r="P17" s="1" t="inlineStr">
         <is>
-          <t>43636501</t>
+          <t>06571347</t>
         </is>
       </c>
       <c r="Q17" s="1" t="inlineStr">
         <is>
-          <t>Av. Brasil 863 departamento 702-A</t>
-        </is>
-      </c>
-      <c r="R17" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">966422784		</t>
-        </is>
-      </c>
+          <t>Mz D Lt 7 Urb. La Estrella</t>
+        </is>
+      </c>
+      <c r="R17" s="1" t="inlineStr"/>
       <c r="S17" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">966422784		</t>
+          <t>969742622</t>
         </is>
       </c>
       <c r="T17" s="1" t="inlineStr">
         <is>
-          <t>victoria.sampi@gmail.com</t>
+          <t>gvidelaf@gmail.com</t>
         </is>
       </c>
       <c r="U17" s="1" t="inlineStr">
@@ -4121,32 +4173,32 @@
       </c>
       <c r="V17" s="1" t="inlineStr">
         <is>
-          <t>JESUS MARIA</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="W17" s="1" t="inlineStr">
         <is>
-          <t>21/07/2024 00:00</t>
+          <t>04/09/2024 00:00</t>
         </is>
       </c>
       <c r="X17" s="1" t="inlineStr">
         <is>
-          <t>21/07/2024 00:00</t>
+          <t>04/09/2024 00:00</t>
         </is>
       </c>
       <c r="Y17" s="1" t="inlineStr">
         <is>
-          <t>SEPARACION</t>
+          <t>CUOTA INICIAL</t>
         </is>
       </c>
       <c r="Z17" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA17" s="1" t="inlineStr">
         <is>
-          <t>3000.00</t>
+          <t>281120.00</t>
         </is>
       </c>
       <c r="AB17" s="1" t="inlineStr">
@@ -4161,12 +4213,12 @@
       </c>
       <c r="AD17" s="1" t="inlineStr">
         <is>
-          <t>3000.00</t>
+          <t>281120.00</t>
         </is>
       </c>
       <c r="AE17" s="1" t="inlineStr">
         <is>
-          <t>3000.00</t>
+          <t>281120.00</t>
         </is>
       </c>
       <c r="AF17" s="1" t="inlineStr">
@@ -4181,7 +4233,7 @@
       </c>
       <c r="AH17" s="1" t="inlineStr">
         <is>
-          <t>Crédito Hipotecario</t>
+          <t>Crédito Directo</t>
         </is>
       </c>
       <c r="AI17" s="1" t="inlineStr">
@@ -4199,14 +4251,10 @@
           <t>TRANSFERENCIA BANCARIA</t>
         </is>
       </c>
-      <c r="AL17" s="1" t="inlineStr">
-        <is>
-          <t>43636501</t>
-        </is>
-      </c>
+      <c r="AL17" s="1" t="inlineStr"/>
       <c r="AM17" s="1" t="inlineStr">
         <is>
-          <t>00998929</t>
+          <t>0953413</t>
         </is>
       </c>
       <c r="AN17" s="1" t="inlineStr">
@@ -4214,11 +4262,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AO17" s="1" t="inlineStr">
-        <is>
-          <t>NO PRECISA</t>
-        </is>
-      </c>
+      <c r="AO17" s="1" t="inlineStr"/>
       <c r="AP17" s="1" t="inlineStr">
         <is>
           <t>4.00</t>
@@ -4246,23 +4290,23 @@
       </c>
       <c r="BC17" s="1" t="inlineStr">
         <is>
-          <t>02/09/2024 14:14</t>
+          <t>31/08/2024 00:00</t>
         </is>
       </c>
       <c r="BD17" s="1" t="inlineStr">
         <is>
-          <t>Kenny Salazar S</t>
+          <t>Carla Michue M</t>
         </is>
       </c>
       <c r="BE17" s="1" t="inlineStr"/>
       <c r="BF17" s="1" t="inlineStr">
         <is>
-          <t>000032</t>
+          <t>000024</t>
         </is>
       </c>
       <c r="BG17" s="1" t="inlineStr">
         <is>
-          <t>02/06/2026 14:50</t>
+          <t>30/06/2026 16:33</t>
         </is>
       </c>
     </row>
@@ -4294,17 +4338,17 @@
       </c>
       <c r="F18" s="1" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>203</t>
         </is>
       </c>
       <c r="G18" s="1" t="inlineStr">
         <is>
-          <t>609100.00</t>
+          <t>654000.00</t>
         </is>
       </c>
       <c r="H18" s="1" t="inlineStr">
         <is>
-          <t>609100.00</t>
+          <t>654000.00</t>
         </is>
       </c>
       <c r="I18" s="1" t="inlineStr">
@@ -4324,47 +4368,43 @@
       </c>
       <c r="L18" s="1" t="inlineStr">
         <is>
-          <t>E 26 - D 20</t>
+          <t>E 12 - D 09</t>
         </is>
       </c>
       <c r="M18" s="1" t="inlineStr">
         <is>
-          <t>64600.00</t>
+          <t>56300.00</t>
         </is>
       </c>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>64600.00</t>
+          <t>56300.00</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr">
         <is>
-          <t>Gilda Victoria Sampi González</t>
+          <t>Gilberto Videla Flores</t>
         </is>
       </c>
       <c r="P18" s="1" t="inlineStr">
         <is>
-          <t>43636501</t>
+          <t>06571347</t>
         </is>
       </c>
       <c r="Q18" s="1" t="inlineStr">
         <is>
-          <t>Av. Brasil 863 departamento 702-A</t>
-        </is>
-      </c>
-      <c r="R18" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">966422784		</t>
-        </is>
-      </c>
+          <t>Mz D Lt 7 Urb. La Estrella</t>
+        </is>
+      </c>
+      <c r="R18" s="1" t="inlineStr"/>
       <c r="S18" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">966422784		</t>
+          <t>969742622</t>
         </is>
       </c>
       <c r="T18" s="1" t="inlineStr">
         <is>
-          <t>victoria.sampi@gmail.com</t>
+          <t>gvidelaf@gmail.com</t>
         </is>
       </c>
       <c r="U18" s="1" t="inlineStr">
@@ -4374,32 +4414,32 @@
       </c>
       <c r="V18" s="1" t="inlineStr">
         <is>
-          <t>JESUS MARIA</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="W18" s="1" t="inlineStr">
         <is>
-          <t>02/09/2024 00:00</t>
+          <t>30/09/2024 00:00</t>
         </is>
       </c>
       <c r="X18" s="1" t="inlineStr">
         <is>
-          <t>02/09/2024 00:00</t>
+          <t>24/09/2024 00:00</t>
         </is>
       </c>
       <c r="Y18" s="1" t="inlineStr">
         <is>
-          <t>CUOTA INICIAL</t>
+          <t>SALDO FINANCIAR</t>
         </is>
       </c>
       <c r="Z18" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA18" s="1" t="inlineStr">
         <is>
-          <t>134740.00</t>
+          <t>248605.00</t>
         </is>
       </c>
       <c r="AB18" s="1" t="inlineStr">
@@ -4414,12 +4454,12 @@
       </c>
       <c r="AD18" s="1" t="inlineStr">
         <is>
-          <t>134740.00</t>
+          <t>248605.00</t>
         </is>
       </c>
       <c r="AE18" s="1" t="inlineStr">
         <is>
-          <t>134740.00</t>
+          <t>248605.00</t>
         </is>
       </c>
       <c r="AF18" s="1" t="inlineStr">
@@ -4434,7 +4474,7 @@
       </c>
       <c r="AH18" s="1" t="inlineStr">
         <is>
-          <t>Crédito Hipotecario</t>
+          <t>Crédito Directo</t>
         </is>
       </c>
       <c r="AI18" s="1" t="inlineStr">
@@ -4452,14 +4492,10 @@
           <t>TRANSFERENCIA BANCARIA</t>
         </is>
       </c>
-      <c r="AL18" s="1" t="inlineStr">
-        <is>
-          <t>43636501</t>
-        </is>
-      </c>
+      <c r="AL18" s="1" t="inlineStr"/>
       <c r="AM18" s="1" t="inlineStr">
         <is>
-          <t>009107870</t>
+          <t>0036913</t>
         </is>
       </c>
       <c r="AN18" s="1" t="inlineStr">
@@ -4467,11 +4503,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AO18" s="1" t="inlineStr">
-        <is>
-          <t>NO PRECISA</t>
-        </is>
-      </c>
+      <c r="AO18" s="1" t="inlineStr"/>
       <c r="AP18" s="1" t="inlineStr">
         <is>
           <t>4.00</t>
@@ -4499,23 +4531,23 @@
       </c>
       <c r="BC18" s="1" t="inlineStr">
         <is>
-          <t>02/09/2024 14:14</t>
+          <t>31/08/2024 00:00</t>
         </is>
       </c>
       <c r="BD18" s="1" t="inlineStr">
         <is>
-          <t>Kenny Salazar S</t>
+          <t>Carla Michue M</t>
         </is>
       </c>
       <c r="BE18" s="1" t="inlineStr"/>
       <c r="BF18" s="1" t="inlineStr">
         <is>
-          <t>000032</t>
+          <t>000024</t>
         </is>
       </c>
       <c r="BG18" s="1" t="inlineStr">
         <is>
-          <t>04/06/2026 09:52</t>
+          <t>30/06/2026 16:48</t>
         </is>
       </c>
     </row>
@@ -4547,49 +4579,77 @@
       </c>
       <c r="F19" s="1" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>104</t>
         </is>
       </c>
       <c r="G19" s="1" t="inlineStr">
         <is>
-          <t>622500.00</t>
+          <t>609100.00</t>
         </is>
       </c>
       <c r="H19" s="1" t="inlineStr">
         <is>
-          <t>622500.00</t>
-        </is>
-      </c>
-      <c r="I19" s="1" t="inlineStr"/>
-      <c r="J19" s="1" t="inlineStr"/>
-      <c r="K19" s="1" t="inlineStr"/>
-      <c r="L19" s="1" t="inlineStr"/>
-      <c r="M19" s="1" t="inlineStr"/>
-      <c r="N19" s="1" t="inlineStr"/>
+          <t>609100.00</t>
+        </is>
+      </c>
+      <c r="I19" s="1" t="inlineStr">
+        <is>
+          <t>Edificio</t>
+        </is>
+      </c>
+      <c r="J19" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K19" s="1" t="inlineStr">
+        <is>
+          <t>Estacionamiento</t>
+        </is>
+      </c>
+      <c r="L19" s="1" t="inlineStr">
+        <is>
+          <t>E 26 - D 20</t>
+        </is>
+      </c>
+      <c r="M19" s="1" t="inlineStr">
+        <is>
+          <t>64600.00</t>
+        </is>
+      </c>
+      <c r="N19" s="1" t="inlineStr">
+        <is>
+          <t>64600.00</t>
+        </is>
+      </c>
       <c r="O19" s="1" t="inlineStr">
         <is>
-          <t>Joseluis Gaspar Zapata Flores</t>
+          <t>Gilda Victoria Sampi González</t>
         </is>
       </c>
       <c r="P19" s="1" t="inlineStr">
         <is>
-          <t>46730672</t>
+          <t>43636501</t>
         </is>
       </c>
       <c r="Q19" s="1" t="inlineStr">
         <is>
-          <t>Jr. Los Clavles 141 P. J  El Progreso 1er Sector</t>
-        </is>
-      </c>
-      <c r="R19" s="1" t="inlineStr"/>
+          <t>Av. Brasil 863 departamento 702-A</t>
+        </is>
+      </c>
+      <c r="R19" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">966422784		</t>
+        </is>
+      </c>
       <c r="S19" s="1" t="inlineStr">
         <is>
-          <t>948041027</t>
+          <t xml:space="preserve">966422784		</t>
         </is>
       </c>
       <c r="T19" s="1" t="inlineStr">
         <is>
-          <t>jlzapata91@gmail.com</t>
+          <t>victoria.sampi@gmail.com</t>
         </is>
       </c>
       <c r="U19" s="1" t="inlineStr">
@@ -4599,22 +4659,22 @@
       </c>
       <c r="V19" s="1" t="inlineStr">
         <is>
-          <t>CARABAYLLO</t>
+          <t>JESUS MARIA</t>
         </is>
       </c>
       <c r="W19" s="1" t="inlineStr">
         <is>
-          <t>06/07/2024 00:00</t>
+          <t>21/07/2024 00:00</t>
         </is>
       </c>
       <c r="X19" s="1" t="inlineStr">
         <is>
-          <t>05/07/2024 00:00</t>
+          <t>21/07/2024 00:00</t>
         </is>
       </c>
       <c r="Y19" s="1" t="inlineStr">
         <is>
-          <t>CUOTA INICIAL</t>
+          <t>SEPARACION</t>
         </is>
       </c>
       <c r="Z19" s="1" t="inlineStr">
@@ -4659,7 +4719,7 @@
       </c>
       <c r="AH19" s="1" t="inlineStr">
         <is>
-          <t>Ahorro</t>
+          <t>Crédito Hipotecario</t>
         </is>
       </c>
       <c r="AI19" s="1" t="inlineStr">
@@ -4677,10 +4737,14 @@
           <t>TRANSFERENCIA BANCARIA</t>
         </is>
       </c>
-      <c r="AL19" s="1" t="inlineStr"/>
+      <c r="AL19" s="1" t="inlineStr">
+        <is>
+          <t>43636501</t>
+        </is>
+      </c>
       <c r="AM19" s="1" t="inlineStr">
         <is>
-          <t>03343387</t>
+          <t>00998929</t>
         </is>
       </c>
       <c r="AN19" s="1" t="inlineStr">
@@ -4688,7 +4752,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AO19" s="1" t="inlineStr"/>
+      <c r="AO19" s="1" t="inlineStr">
+        <is>
+          <t>NO PRECISA</t>
+        </is>
+      </c>
       <c r="AP19" s="1" t="inlineStr">
         <is>
           <t>4.00</t>
@@ -4716,23 +4784,23 @@
       </c>
       <c r="BC19" s="1" t="inlineStr">
         <is>
-          <t>15/07/2024 15:43</t>
+          <t>02/09/2024 14:14</t>
         </is>
       </c>
       <c r="BD19" s="1" t="inlineStr">
         <is>
-          <t>Carla Michue M</t>
+          <t>Kenny Salazar S</t>
         </is>
       </c>
       <c r="BE19" s="1" t="inlineStr"/>
       <c r="BF19" s="1" t="inlineStr">
         <is>
-          <t>000006</t>
+          <t>000032</t>
         </is>
       </c>
       <c r="BG19" s="1" t="inlineStr">
         <is>
-          <t>29/06/2026 01:05</t>
+          <t>02/06/2026 14:50</t>
         </is>
       </c>
     </row>
@@ -4764,49 +4832,77 @@
       </c>
       <c r="F20" s="1" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>104</t>
         </is>
       </c>
       <c r="G20" s="1" t="inlineStr">
         <is>
-          <t>622500.00</t>
+          <t>609100.00</t>
         </is>
       </c>
       <c r="H20" s="1" t="inlineStr">
         <is>
-          <t>622500.00</t>
-        </is>
-      </c>
-      <c r="I20" s="1" t="inlineStr"/>
-      <c r="J20" s="1" t="inlineStr"/>
-      <c r="K20" s="1" t="inlineStr"/>
-      <c r="L20" s="1" t="inlineStr"/>
-      <c r="M20" s="1" t="inlineStr"/>
-      <c r="N20" s="1" t="inlineStr"/>
+          <t>609100.00</t>
+        </is>
+      </c>
+      <c r="I20" s="1" t="inlineStr">
+        <is>
+          <t>Edificio</t>
+        </is>
+      </c>
+      <c r="J20" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K20" s="1" t="inlineStr">
+        <is>
+          <t>Estacionamiento</t>
+        </is>
+      </c>
+      <c r="L20" s="1" t="inlineStr">
+        <is>
+          <t>E 26 - D 20</t>
+        </is>
+      </c>
+      <c r="M20" s="1" t="inlineStr">
+        <is>
+          <t>64600.00</t>
+        </is>
+      </c>
+      <c r="N20" s="1" t="inlineStr">
+        <is>
+          <t>64600.00</t>
+        </is>
+      </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
-          <t>Joseluis Gaspar Zapata Flores</t>
+          <t>Gilda Victoria Sampi González</t>
         </is>
       </c>
       <c r="P20" s="1" t="inlineStr">
         <is>
-          <t>46730672</t>
+          <t>43636501</t>
         </is>
       </c>
       <c r="Q20" s="1" t="inlineStr">
         <is>
-          <t>Jr. Los Clavles 141 P. J  El Progreso 1er Sector</t>
-        </is>
-      </c>
-      <c r="R20" s="1" t="inlineStr"/>
+          <t>Av. Brasil 863 departamento 702-A</t>
+        </is>
+      </c>
+      <c r="R20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">966422784		</t>
+        </is>
+      </c>
       <c r="S20" s="1" t="inlineStr">
         <is>
-          <t>948041027</t>
+          <t xml:space="preserve">966422784		</t>
         </is>
       </c>
       <c r="T20" s="1" t="inlineStr">
         <is>
-          <t>jlzapata91@gmail.com</t>
+          <t>victoria.sampi@gmail.com</t>
         </is>
       </c>
       <c r="U20" s="1" t="inlineStr">
@@ -4816,17 +4912,17 @@
       </c>
       <c r="V20" s="1" t="inlineStr">
         <is>
-          <t>CARABAYLLO</t>
+          <t>JESUS MARIA</t>
         </is>
       </c>
       <c r="W20" s="1" t="inlineStr">
         <is>
-          <t>15/07/2024 00:00</t>
+          <t>02/09/2024 00:00</t>
         </is>
       </c>
       <c r="X20" s="1" t="inlineStr">
         <is>
-          <t>15/07/2024 00:00</t>
+          <t>02/09/2024 00:00</t>
         </is>
       </c>
       <c r="Y20" s="1" t="inlineStr">
@@ -4836,12 +4932,12 @@
       </c>
       <c r="Z20" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA20" s="1" t="inlineStr">
         <is>
-          <t>20000.00</t>
+          <t>134740.00</t>
         </is>
       </c>
       <c r="AB20" s="1" t="inlineStr">
@@ -4856,12 +4952,12 @@
       </c>
       <c r="AD20" s="1" t="inlineStr">
         <is>
-          <t>20000.00</t>
+          <t>134740.00</t>
         </is>
       </c>
       <c r="AE20" s="1" t="inlineStr">
         <is>
-          <t>20000.00</t>
+          <t>134740.00</t>
         </is>
       </c>
       <c r="AF20" s="1" t="inlineStr">
@@ -4876,7 +4972,7 @@
       </c>
       <c r="AH20" s="1" t="inlineStr">
         <is>
-          <t>Ahorro</t>
+          <t>Crédito Hipotecario</t>
         </is>
       </c>
       <c r="AI20" s="1" t="inlineStr">
@@ -4894,10 +4990,14 @@
           <t>TRANSFERENCIA BANCARIA</t>
         </is>
       </c>
-      <c r="AL20" s="1" t="inlineStr"/>
+      <c r="AL20" s="1" t="inlineStr">
+        <is>
+          <t>43636501</t>
+        </is>
+      </c>
       <c r="AM20" s="1" t="inlineStr">
         <is>
-          <t>7844655656315</t>
+          <t>009107870</t>
         </is>
       </c>
       <c r="AN20" s="1" t="inlineStr">
@@ -4905,7 +5005,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AO20" s="1" t="inlineStr"/>
+      <c r="AO20" s="1" t="inlineStr">
+        <is>
+          <t>NO PRECISA</t>
+        </is>
+      </c>
       <c r="AP20" s="1" t="inlineStr">
         <is>
           <t>4.00</t>
@@ -4933,23 +5037,23 @@
       </c>
       <c r="BC20" s="1" t="inlineStr">
         <is>
-          <t>15/07/2024 15:43</t>
+          <t>02/09/2024 14:14</t>
         </is>
       </c>
       <c r="BD20" s="1" t="inlineStr">
         <is>
-          <t>Carla Michue M</t>
+          <t>Kenny Salazar S</t>
         </is>
       </c>
       <c r="BE20" s="1" t="inlineStr"/>
       <c r="BF20" s="1" t="inlineStr">
         <is>
-          <t>000006</t>
+          <t>000032</t>
         </is>
       </c>
       <c r="BG20" s="1" t="inlineStr">
         <is>
-          <t>29/06/2026 01:06</t>
+          <t>04/06/2026 09:52</t>
         </is>
       </c>
     </row>
@@ -5038,12 +5142,12 @@
       </c>
       <c r="W21" s="1" t="inlineStr">
         <is>
-          <t>31/12/2024 00:00</t>
+          <t>06/07/2024 00:00</t>
         </is>
       </c>
       <c r="X21" s="1" t="inlineStr">
         <is>
-          <t>06/03/2025 00:00</t>
+          <t>05/07/2024 00:00</t>
         </is>
       </c>
       <c r="Y21" s="1" t="inlineStr">
@@ -5053,12 +5157,12 @@
       </c>
       <c r="Z21" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA21" s="1" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3000.00</t>
         </is>
       </c>
       <c r="AB21" s="1" t="inlineStr">
@@ -5073,12 +5177,12 @@
       </c>
       <c r="AD21" s="1" t="inlineStr">
         <is>
-          <t>67000.00</t>
+          <t>3000.00</t>
         </is>
       </c>
       <c r="AE21" s="1" t="inlineStr">
         <is>
-          <t>65000.00</t>
+          <t>3000.00</t>
         </is>
       </c>
       <c r="AF21" s="1" t="inlineStr">
@@ -5114,7 +5218,7 @@
       <c r="AL21" s="1" t="inlineStr"/>
       <c r="AM21" s="1" t="inlineStr">
         <is>
-          <t>u26563</t>
+          <t>03343387</t>
         </is>
       </c>
       <c r="AN21" s="1" t="inlineStr">
@@ -5166,7 +5270,7 @@
       </c>
       <c r="BG21" s="1" t="inlineStr">
         <is>
-          <t>29/06/2026 01:07</t>
+          <t>29/06/2026 01:05</t>
         </is>
       </c>
     </row>
@@ -5255,12 +5359,12 @@
       </c>
       <c r="W22" s="1" t="inlineStr">
         <is>
-          <t>31/12/2024 00:00</t>
+          <t>15/07/2024 00:00</t>
         </is>
       </c>
       <c r="X22" s="1" t="inlineStr">
         <is>
-          <t>29/06/2026 00:00</t>
+          <t>15/07/2024 00:00</t>
         </is>
       </c>
       <c r="Y22" s="1" t="inlineStr">
@@ -5270,12 +5374,12 @@
       </c>
       <c r="Z22" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA22" s="1" t="inlineStr">
         <is>
-          <t>67000.00</t>
+          <t>20000.00</t>
         </is>
       </c>
       <c r="AB22" s="1" t="inlineStr">
@@ -5290,12 +5394,12 @@
       </c>
       <c r="AD22" s="1" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>20000.00</t>
         </is>
       </c>
       <c r="AE22" s="1" t="inlineStr">
         <is>
-          <t>2000.00</t>
+          <t>20000.00</t>
         </is>
       </c>
       <c r="AF22" s="1" t="inlineStr">
@@ -5331,7 +5435,7 @@
       <c r="AL22" s="1" t="inlineStr"/>
       <c r="AM22" s="1" t="inlineStr">
         <is>
-          <t>7844655541508</t>
+          <t>7844655656315</t>
         </is>
       </c>
       <c r="AN22" s="1" t="inlineStr">
@@ -5383,7 +5487,7 @@
       </c>
       <c r="BG22" s="1" t="inlineStr">
         <is>
-          <t>29/06/2026 01:08</t>
+          <t>29/06/2026 01:06</t>
         </is>
       </c>
     </row>
@@ -5415,17 +5519,17 @@
       </c>
       <c r="F23" s="1" t="inlineStr">
         <is>
-          <t>501</t>
+          <t>201</t>
         </is>
       </c>
       <c r="G23" s="1" t="inlineStr">
         <is>
-          <t>612000.00</t>
+          <t>622500.00</t>
         </is>
       </c>
       <c r="H23" s="1" t="inlineStr">
         <is>
-          <t>612000.00</t>
+          <t>622500.00</t>
         </is>
       </c>
       <c r="I23" s="1" t="inlineStr"/>
@@ -5436,63 +5540,63 @@
       <c r="N23" s="1" t="inlineStr"/>
       <c r="O23" s="1" t="inlineStr">
         <is>
-          <t>Juan Carlos Ángeles Milla</t>
+          <t>Joseluis Gaspar Zapata Flores</t>
         </is>
       </c>
       <c r="P23" s="1" t="inlineStr">
         <is>
-          <t>32403305</t>
+          <t>46730672</t>
         </is>
       </c>
       <c r="Q23" s="1" t="inlineStr">
         <is>
-          <t>Av. Miraflores 218</t>
+          <t>Jr. Los Clavles 141 P. J  El Progreso 1er Sector</t>
         </is>
       </c>
       <c r="R23" s="1" t="inlineStr"/>
       <c r="S23" s="1" t="inlineStr">
         <is>
-          <t>942097700</t>
+          <t>948041027</t>
         </is>
       </c>
       <c r="T23" s="1" t="inlineStr">
         <is>
-          <t>Vidang72@hotmail.com</t>
+          <t>jlzapata91@gmail.com</t>
         </is>
       </c>
       <c r="U23" s="1" t="inlineStr">
         <is>
-          <t>HUAYLAS</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="V23" s="1" t="inlineStr">
         <is>
-          <t>HUAYLAS</t>
+          <t>CARABAYLLO</t>
         </is>
       </c>
       <c r="W23" s="1" t="inlineStr">
         <is>
-          <t>16/08/2024 00:00</t>
+          <t>31/12/2024 00:00</t>
         </is>
       </c>
       <c r="X23" s="1" t="inlineStr">
         <is>
-          <t>16/08/2024 00:00</t>
+          <t>06/03/2025 00:00</t>
         </is>
       </c>
       <c r="Y23" s="1" t="inlineStr">
         <is>
-          <t>SEPARACION</t>
+          <t>CUOTA INICIAL</t>
         </is>
       </c>
       <c r="Z23" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA23" s="1" t="inlineStr">
         <is>
-          <t>3000.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB23" s="1" t="inlineStr">
@@ -5507,12 +5611,12 @@
       </c>
       <c r="AD23" s="1" t="inlineStr">
         <is>
-          <t>3000.00</t>
+          <t>67000.00</t>
         </is>
       </c>
       <c r="AE23" s="1" t="inlineStr">
         <is>
-          <t>3000.00</t>
+          <t>65000.00</t>
         </is>
       </c>
       <c r="AF23" s="1" t="inlineStr">
@@ -5545,14 +5649,10 @@
           <t>TRANSFERENCIA BANCARIA</t>
         </is>
       </c>
-      <c r="AL23" s="1" t="inlineStr">
-        <is>
-          <t>32403305</t>
-        </is>
-      </c>
+      <c r="AL23" s="1" t="inlineStr"/>
       <c r="AM23" s="1" t="inlineStr">
         <is>
-          <t>02431073</t>
+          <t>u26563</t>
         </is>
       </c>
       <c r="AN23" s="1" t="inlineStr">
@@ -5560,14 +5660,10 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AO23" s="1" t="inlineStr">
-        <is>
-          <t>NO PRECISA</t>
-        </is>
-      </c>
+      <c r="AO23" s="1" t="inlineStr"/>
       <c r="AP23" s="1" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="AQ23" s="1" t="inlineStr">
@@ -5592,7 +5688,7 @@
       </c>
       <c r="BC23" s="1" t="inlineStr">
         <is>
-          <t>17/08/2024 00:00</t>
+          <t>15/07/2024 15:43</t>
         </is>
       </c>
       <c r="BD23" s="1" t="inlineStr">
@@ -5603,12 +5699,12 @@
       <c r="BE23" s="1" t="inlineStr"/>
       <c r="BF23" s="1" t="inlineStr">
         <is>
-          <t>000021</t>
+          <t>000006</t>
         </is>
       </c>
       <c r="BG23" s="1" t="inlineStr">
         <is>
-          <t>29/05/2026 12:21</t>
+          <t>29/06/2026 01:07</t>
         </is>
       </c>
     </row>
@@ -5640,17 +5736,17 @@
       </c>
       <c r="F24" s="1" t="inlineStr">
         <is>
-          <t>501</t>
+          <t>201</t>
         </is>
       </c>
       <c r="G24" s="1" t="inlineStr">
         <is>
-          <t>612000.00</t>
+          <t>622500.00</t>
         </is>
       </c>
       <c r="H24" s="1" t="inlineStr">
         <is>
-          <t>612000.00</t>
+          <t>622500.00</t>
         </is>
       </c>
       <c r="I24" s="1" t="inlineStr"/>
@@ -5661,48 +5757,48 @@
       <c r="N24" s="1" t="inlineStr"/>
       <c r="O24" s="1" t="inlineStr">
         <is>
-          <t>Juan Carlos Ángeles Milla</t>
+          <t>Joseluis Gaspar Zapata Flores</t>
         </is>
       </c>
       <c r="P24" s="1" t="inlineStr">
         <is>
-          <t>32403305</t>
+          <t>46730672</t>
         </is>
       </c>
       <c r="Q24" s="1" t="inlineStr">
         <is>
-          <t>Av. Miraflores 218</t>
+          <t>Jr. Los Clavles 141 P. J  El Progreso 1er Sector</t>
         </is>
       </c>
       <c r="R24" s="1" t="inlineStr"/>
       <c r="S24" s="1" t="inlineStr">
         <is>
-          <t>942097700</t>
+          <t>948041027</t>
         </is>
       </c>
       <c r="T24" s="1" t="inlineStr">
         <is>
-          <t>Vidang72@hotmail.com</t>
+          <t>jlzapata91@gmail.com</t>
         </is>
       </c>
       <c r="U24" s="1" t="inlineStr">
         <is>
-          <t>HUAYLAS</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="V24" s="1" t="inlineStr">
         <is>
-          <t>HUAYLAS</t>
+          <t>CARABAYLLO</t>
         </is>
       </c>
       <c r="W24" s="1" t="inlineStr">
         <is>
-          <t>06/09/2024 00:00</t>
+          <t>31/12/2024 00:00</t>
         </is>
       </c>
       <c r="X24" s="1" t="inlineStr">
         <is>
-          <t>06/09/2024 00:00</t>
+          <t>29/06/2026 00:00</t>
         </is>
       </c>
       <c r="Y24" s="1" t="inlineStr">
@@ -5712,12 +5808,12 @@
       </c>
       <c r="Z24" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA24" s="1" t="inlineStr">
         <is>
-          <t>29500.00</t>
+          <t>67000.00</t>
         </is>
       </c>
       <c r="AB24" s="1" t="inlineStr">
@@ -5732,12 +5828,12 @@
       </c>
       <c r="AD24" s="1" t="inlineStr">
         <is>
-          <t>29500.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AE24" s="1" t="inlineStr">
         <is>
-          <t>29500.00</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="AF24" s="1" t="inlineStr">
@@ -5770,14 +5866,10 @@
           <t>TRANSFERENCIA BANCARIA</t>
         </is>
       </c>
-      <c r="AL24" s="1" t="inlineStr">
-        <is>
-          <t>32403305</t>
-        </is>
-      </c>
+      <c r="AL24" s="1" t="inlineStr"/>
       <c r="AM24" s="1" t="inlineStr">
         <is>
-          <t>0500010059</t>
+          <t>7844655541508</t>
         </is>
       </c>
       <c r="AN24" s="1" t="inlineStr">
@@ -5785,14 +5877,10 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AO24" s="1" t="inlineStr">
-        <is>
-          <t>NO PRECISA</t>
-        </is>
-      </c>
+      <c r="AO24" s="1" t="inlineStr"/>
       <c r="AP24" s="1" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="AQ24" s="1" t="inlineStr">
@@ -5817,7 +5905,7 @@
       </c>
       <c r="BC24" s="1" t="inlineStr">
         <is>
-          <t>17/08/2024 00:00</t>
+          <t>15/07/2024 15:43</t>
         </is>
       </c>
       <c r="BD24" s="1" t="inlineStr">
@@ -5828,12 +5916,12 @@
       <c r="BE24" s="1" t="inlineStr"/>
       <c r="BF24" s="1" t="inlineStr">
         <is>
-          <t>000021</t>
+          <t>000006</t>
         </is>
       </c>
       <c r="BG24" s="1" t="inlineStr">
         <is>
-          <t>29/05/2026 12:21</t>
+          <t>29/06/2026 01:08</t>
         </is>
       </c>
     </row>
@@ -5922,27 +6010,27 @@
       </c>
       <c r="W25" s="1" t="inlineStr">
         <is>
-          <t>31/12/2024 00:00</t>
+          <t>16/08/2024 00:00</t>
         </is>
       </c>
       <c r="X25" s="1" t="inlineStr">
         <is>
-          <t>27/12/2024 00:00</t>
+          <t>16/08/2024 00:00</t>
         </is>
       </c>
       <c r="Y25" s="1" t="inlineStr">
         <is>
-          <t>CUOTA INICIAL</t>
+          <t>SEPARACION</t>
         </is>
       </c>
       <c r="Z25" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA25" s="1" t="inlineStr">
         <is>
-          <t>29500.00</t>
+          <t>3000.00</t>
         </is>
       </c>
       <c r="AB25" s="1" t="inlineStr">
@@ -5957,12 +6045,12 @@
       </c>
       <c r="AD25" s="1" t="inlineStr">
         <is>
-          <t>29500.00</t>
+          <t>3000.00</t>
         </is>
       </c>
       <c r="AE25" s="1" t="inlineStr">
         <is>
-          <t>29500.00</t>
+          <t>3000.00</t>
         </is>
       </c>
       <c r="AF25" s="1" t="inlineStr">
@@ -6002,7 +6090,7 @@
       </c>
       <c r="AM25" s="1" t="inlineStr">
         <is>
-          <t>028925</t>
+          <t>02431073</t>
         </is>
       </c>
       <c r="AN25" s="1" t="inlineStr">
@@ -6090,17 +6178,17 @@
       </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>501</t>
         </is>
       </c>
       <c r="G26" s="1" t="inlineStr">
         <is>
-          <t>654000.00</t>
+          <t>612000.00</t>
         </is>
       </c>
       <c r="H26" s="1" t="inlineStr">
         <is>
-          <t>654000.00</t>
+          <t>612000.00</t>
         </is>
       </c>
       <c r="I26" s="1" t="inlineStr"/>
@@ -6111,63 +6199,63 @@
       <c r="N26" s="1" t="inlineStr"/>
       <c r="O26" s="1" t="inlineStr">
         <is>
-          <t>Liliana Lucila Luciano Claros</t>
+          <t>Juan Carlos Ángeles Milla</t>
         </is>
       </c>
       <c r="P26" s="1" t="inlineStr">
         <is>
-          <t>15764694</t>
+          <t>32403305</t>
         </is>
       </c>
       <c r="Q26" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">MZ M5 – Lt. 7 urb. Paseo del Mar </t>
+          <t>Av. Miraflores 218</t>
         </is>
       </c>
       <c r="R26" s="1" t="inlineStr"/>
       <c r="S26" s="1" t="inlineStr">
         <is>
-          <t>982406857</t>
+          <t>942097700</t>
         </is>
       </c>
       <c r="T26" s="1" t="inlineStr">
         <is>
-          <t>liliana31_micaela@hotmail.com</t>
+          <t>Vidang72@hotmail.com</t>
         </is>
       </c>
       <c r="U26" s="1" t="inlineStr">
         <is>
-          <t>SANTA</t>
+          <t>HUAYLAS</t>
         </is>
       </c>
       <c r="V26" s="1" t="inlineStr">
         <is>
-          <t>NUEVO CHIMBOTE</t>
+          <t>HUAYLAS</t>
         </is>
       </c>
       <c r="W26" s="1" t="inlineStr">
         <is>
-          <t>21/10/2024 00:00</t>
+          <t>06/09/2024 00:00</t>
         </is>
       </c>
       <c r="X26" s="1" t="inlineStr">
         <is>
-          <t>21/10/2024 00:00</t>
+          <t>06/09/2024 00:00</t>
         </is>
       </c>
       <c r="Y26" s="1" t="inlineStr">
         <is>
-          <t>SEPARACION</t>
+          <t>CUOTA INICIAL</t>
         </is>
       </c>
       <c r="Z26" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA26" s="1" t="inlineStr">
         <is>
-          <t>3000.00</t>
+          <t>29500.00</t>
         </is>
       </c>
       <c r="AB26" s="1" t="inlineStr">
@@ -6182,12 +6270,12 @@
       </c>
       <c r="AD26" s="1" t="inlineStr">
         <is>
-          <t>3000.00</t>
+          <t>29500.00</t>
         </is>
       </c>
       <c r="AE26" s="1" t="inlineStr">
         <is>
-          <t>3000.00</t>
+          <t>29500.00</t>
         </is>
       </c>
       <c r="AF26" s="1" t="inlineStr">
@@ -6202,7 +6290,7 @@
       </c>
       <c r="AH26" s="1" t="inlineStr">
         <is>
-          <t>Crédito Hipotecario</t>
+          <t>Ahorro</t>
         </is>
       </c>
       <c r="AI26" s="1" t="inlineStr">
@@ -6217,17 +6305,17 @@
       </c>
       <c r="AK26" s="1" t="inlineStr">
         <is>
-          <t>EFECTIVO</t>
+          <t>TRANSFERENCIA BANCARIA</t>
         </is>
       </c>
       <c r="AL26" s="1" t="inlineStr">
         <is>
-          <t>15764694</t>
+          <t>32403305</t>
         </is>
       </c>
       <c r="AM26" s="1" t="inlineStr">
         <is>
-          <t>0500010056</t>
+          <t>0500010059</t>
         </is>
       </c>
       <c r="AN26" s="1" t="inlineStr">
@@ -6267,7 +6355,7 @@
       </c>
       <c r="BC26" s="1" t="inlineStr">
         <is>
-          <t>29/10/2024 16:25</t>
+          <t>17/08/2024 00:00</t>
         </is>
       </c>
       <c r="BD26" s="1" t="inlineStr">
@@ -6278,12 +6366,12 @@
       <c r="BE26" s="1" t="inlineStr"/>
       <c r="BF26" s="1" t="inlineStr">
         <is>
-          <t>000001</t>
+          <t>000021</t>
         </is>
       </c>
       <c r="BG26" s="1" t="inlineStr">
         <is>
-          <t>29/05/2026 12:20</t>
+          <t>29/05/2026 12:21</t>
         </is>
       </c>
     </row>
@@ -6315,17 +6403,17 @@
       </c>
       <c r="F27" s="1" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>501</t>
         </is>
       </c>
       <c r="G27" s="1" t="inlineStr">
         <is>
-          <t>654000.00</t>
+          <t>612000.00</t>
         </is>
       </c>
       <c r="H27" s="1" t="inlineStr">
         <is>
-          <t>654000.00</t>
+          <t>612000.00</t>
         </is>
       </c>
       <c r="I27" s="1" t="inlineStr"/>
@@ -6336,48 +6424,48 @@
       <c r="N27" s="1" t="inlineStr"/>
       <c r="O27" s="1" t="inlineStr">
         <is>
-          <t>Liliana Lucila Luciano Claros</t>
+          <t>Juan Carlos Ángeles Milla</t>
         </is>
       </c>
       <c r="P27" s="1" t="inlineStr">
         <is>
-          <t>15764694</t>
+          <t>32403305</t>
         </is>
       </c>
       <c r="Q27" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">MZ M5 – Lt. 7 urb. Paseo del Mar </t>
+          <t>Av. Miraflores 218</t>
         </is>
       </c>
       <c r="R27" s="1" t="inlineStr"/>
       <c r="S27" s="1" t="inlineStr">
         <is>
-          <t>982406857</t>
+          <t>942097700</t>
         </is>
       </c>
       <c r="T27" s="1" t="inlineStr">
         <is>
-          <t>liliana31_micaela@hotmail.com</t>
+          <t>Vidang72@hotmail.com</t>
         </is>
       </c>
       <c r="U27" s="1" t="inlineStr">
         <is>
-          <t>SANTA</t>
+          <t>HUAYLAS</t>
         </is>
       </c>
       <c r="V27" s="1" t="inlineStr">
         <is>
-          <t>NUEVO CHIMBOTE</t>
+          <t>HUAYLAS</t>
         </is>
       </c>
       <c r="W27" s="1" t="inlineStr">
         <is>
-          <t>23/11/2024 00:00</t>
+          <t>31/12/2024 00:00</t>
         </is>
       </c>
       <c r="X27" s="1" t="inlineStr">
         <is>
-          <t>23/11/2024 00:00</t>
+          <t>27/12/2024 00:00</t>
         </is>
       </c>
       <c r="Y27" s="1" t="inlineStr">
@@ -6387,12 +6475,12 @@
       </c>
       <c r="Z27" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA27" s="1" t="inlineStr">
         <is>
-          <t>97800.00</t>
+          <t>29500.00</t>
         </is>
       </c>
       <c r="AB27" s="1" t="inlineStr">
@@ -6407,12 +6495,12 @@
       </c>
       <c r="AD27" s="1" t="inlineStr">
         <is>
-          <t>97800.00</t>
+          <t>29500.00</t>
         </is>
       </c>
       <c r="AE27" s="1" t="inlineStr">
         <is>
-          <t>97800.00</t>
+          <t>29500.00</t>
         </is>
       </c>
       <c r="AF27" s="1" t="inlineStr">
@@ -6427,7 +6515,7 @@
       </c>
       <c r="AH27" s="1" t="inlineStr">
         <is>
-          <t>Crédito Hipotecario</t>
+          <t>Ahorro</t>
         </is>
       </c>
       <c r="AI27" s="1" t="inlineStr">
@@ -6445,10 +6533,14 @@
           <t>TRANSFERENCIA BANCARIA</t>
         </is>
       </c>
-      <c r="AL27" s="1" t="inlineStr"/>
+      <c r="AL27" s="1" t="inlineStr">
+        <is>
+          <t>32403305</t>
+        </is>
+      </c>
       <c r="AM27" s="1" t="inlineStr">
         <is>
-          <t>1410</t>
+          <t>028925</t>
         </is>
       </c>
       <c r="AN27" s="1" t="inlineStr">
@@ -6456,7 +6548,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AO27" s="1" t="inlineStr"/>
+      <c r="AO27" s="1" t="inlineStr">
+        <is>
+          <t>NO PRECISA</t>
+        </is>
+      </c>
       <c r="AP27" s="1" t="inlineStr">
         <is>
           <t>1.00</t>
@@ -6479,12 +6575,12 @@
       <c r="BA27" s="1" t="inlineStr"/>
       <c r="BB27" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="BC27" s="1" t="inlineStr">
         <is>
-          <t>29/10/2024 16:25</t>
+          <t>17/08/2024 00:00</t>
         </is>
       </c>
       <c r="BD27" s="1" t="inlineStr">
@@ -6495,12 +6591,12 @@
       <c r="BE27" s="1" t="inlineStr"/>
       <c r="BF27" s="1" t="inlineStr">
         <is>
-          <t>000001</t>
+          <t>000021</t>
         </is>
       </c>
       <c r="BG27" s="1" t="inlineStr">
         <is>
-          <t>29/05/2026 12:20</t>
+          <t>29/05/2026 12:21</t>
         </is>
       </c>
     </row>
@@ -6589,27 +6685,27 @@
       </c>
       <c r="W28" s="1" t="inlineStr">
         <is>
-          <t>31/12/2024 00:00</t>
+          <t>21/10/2024 00:00</t>
         </is>
       </c>
       <c r="X28" s="1" t="inlineStr">
         <is>
-          <t>05/12/2024 00:00</t>
+          <t>21/10/2024 00:00</t>
         </is>
       </c>
       <c r="Y28" s="1" t="inlineStr">
         <is>
-          <t>CUOTA INICIAL</t>
+          <t>SEPARACION</t>
         </is>
       </c>
       <c r="Z28" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA28" s="1" t="inlineStr">
         <is>
-          <t>30000.00</t>
+          <t>3000.00</t>
         </is>
       </c>
       <c r="AB28" s="1" t="inlineStr">
@@ -6624,12 +6720,12 @@
       </c>
       <c r="AD28" s="1" t="inlineStr">
         <is>
-          <t>30000.00</t>
+          <t>3000.00</t>
         </is>
       </c>
       <c r="AE28" s="1" t="inlineStr">
         <is>
-          <t>30000.00</t>
+          <t>3000.00</t>
         </is>
       </c>
       <c r="AF28" s="1" t="inlineStr">
@@ -6659,7 +6755,7 @@
       </c>
       <c r="AK28" s="1" t="inlineStr">
         <is>
-          <t>DEPOSITO EN CUENTA</t>
+          <t>EFECTIVO</t>
         </is>
       </c>
       <c r="AL28" s="1" t="inlineStr">
@@ -6669,7 +6765,7 @@
       </c>
       <c r="AM28" s="1" t="inlineStr">
         <is>
-          <t>05000010069</t>
+          <t>0500010056</t>
         </is>
       </c>
       <c r="AN28" s="1" t="inlineStr">
@@ -6814,23 +6910,27 @@
       </c>
       <c r="W29" s="1" t="inlineStr">
         <is>
-          <t>31/12/2024 00:00</t>
-        </is>
-      </c>
-      <c r="X29" s="1" t="inlineStr"/>
+          <t>23/11/2024 00:00</t>
+        </is>
+      </c>
+      <c r="X29" s="1" t="inlineStr">
+        <is>
+          <t>23/11/2024 00:00</t>
+        </is>
+      </c>
       <c r="Y29" s="1" t="inlineStr">
         <is>
-          <t>SALDO FINANCIAR</t>
+          <t>CUOTA INICIAL</t>
         </is>
       </c>
       <c r="Z29" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA29" s="1" t="inlineStr">
         <is>
-          <t>523200.00</t>
+          <t>97800.00</t>
         </is>
       </c>
       <c r="AB29" s="1" t="inlineStr">
@@ -6845,40 +6945,64 @@
       </c>
       <c r="AD29" s="1" t="inlineStr">
         <is>
-          <t>523200.00</t>
+          <t>97800.00</t>
         </is>
       </c>
       <c r="AE29" s="1" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>97800.00</t>
         </is>
       </c>
       <c r="AF29" s="1" t="inlineStr">
         <is>
-          <t>523200.00</t>
-        </is>
-      </c>
-      <c r="AG29" s="1" t="inlineStr"/>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AG29" s="1" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
       <c r="AH29" s="1" t="inlineStr">
         <is>
           <t>Crédito Hipotecario</t>
         </is>
       </c>
-      <c r="AI29" s="1" t="inlineStr"/>
-      <c r="AJ29" s="1" t="inlineStr"/>
-      <c r="AK29" s="1" t="inlineStr"/>
+      <c r="AI29" s="1" t="inlineStr">
+        <is>
+          <t>Scotiabank Perú</t>
+        </is>
+      </c>
+      <c r="AJ29" s="1" t="inlineStr">
+        <is>
+          <t>000-2768484</t>
+        </is>
+      </c>
+      <c r="AK29" s="1" t="inlineStr">
+        <is>
+          <t>TRANSFERENCIA BANCARIA</t>
+        </is>
+      </c>
       <c r="AL29" s="1" t="inlineStr"/>
-      <c r="AM29" s="1" t="inlineStr"/>
+      <c r="AM29" s="1" t="inlineStr">
+        <is>
+          <t>12007725</t>
+        </is>
+      </c>
       <c r="AN29" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
       <c r="AO29" s="1" t="inlineStr"/>
-      <c r="AP29" s="1" t="inlineStr"/>
+      <c r="AP29" s="1" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
       <c r="AQ29" s="1" t="inlineStr">
         <is>
-          <t>VENCIDO</t>
+          <t>CANCELADO</t>
         </is>
       </c>
       <c r="AR29" s="1" t="inlineStr"/>
@@ -6893,7 +7017,7 @@
       <c r="BA29" s="1" t="inlineStr"/>
       <c r="BB29" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="BC29" s="1" t="inlineStr">
@@ -6912,7 +7036,11 @@
           <t>000001</t>
         </is>
       </c>
-      <c r="BG29" s="1" t="inlineStr"/>
+      <c r="BG29" s="1" t="inlineStr">
+        <is>
+          <t>07/07/2026 09:30</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
@@ -6942,7 +7070,7 @@
       </c>
       <c r="F30" s="1" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>403</t>
         </is>
       </c>
       <c r="G30" s="1" t="inlineStr">
@@ -6955,95 +7083,71 @@
           <t>654000.00</t>
         </is>
       </c>
-      <c r="I30" s="1" t="inlineStr">
-        <is>
-          <t>Edificio</t>
-        </is>
-      </c>
-      <c r="J30" s="1" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K30" s="1" t="inlineStr">
-        <is>
-          <t>Estacionamiento</t>
-        </is>
-      </c>
-      <c r="L30" s="1" t="inlineStr">
-        <is>
-          <t>E 37 - D 28</t>
-        </is>
-      </c>
-      <c r="M30" s="1" t="inlineStr">
-        <is>
-          <t>52000.00</t>
-        </is>
-      </c>
-      <c r="N30" s="1" t="inlineStr">
-        <is>
-          <t>52000.00</t>
-        </is>
-      </c>
+      <c r="I30" s="1" t="inlineStr"/>
+      <c r="J30" s="1" t="inlineStr"/>
+      <c r="K30" s="1" t="inlineStr"/>
+      <c r="L30" s="1" t="inlineStr"/>
+      <c r="M30" s="1" t="inlineStr"/>
+      <c r="N30" s="1" t="inlineStr"/>
       <c r="O30" s="1" t="inlineStr">
         <is>
-          <t>Luis Alberto Ovalle Huamanguilla</t>
+          <t>Liliana Lucila Luciano Claros</t>
         </is>
       </c>
       <c r="P30" s="1" t="inlineStr">
         <is>
-          <t>43953371</t>
+          <t>15764694</t>
         </is>
       </c>
       <c r="Q30" s="1" t="inlineStr">
         <is>
-          <t>JR. NAPO NRO. 821</t>
+          <t xml:space="preserve">MZ M5 – Lt. 7 urb. Paseo del Mar </t>
         </is>
       </c>
       <c r="R30" s="1" t="inlineStr"/>
       <c r="S30" s="1" t="inlineStr">
         <is>
-          <t>992764943</t>
+          <t>982406857</t>
         </is>
       </c>
       <c r="T30" s="1" t="inlineStr">
         <is>
-          <t>aovalle2212@gmail.com</t>
+          <t>liliana31_micaela@hotmail.com</t>
         </is>
       </c>
       <c r="U30" s="1" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>SANTA</t>
         </is>
       </c>
       <c r="V30" s="1" t="inlineStr">
         <is>
-          <t>BREÑA</t>
+          <t>NUEVO CHIMBOTE</t>
         </is>
       </c>
       <c r="W30" s="1" t="inlineStr">
         <is>
-          <t>04/07/2024 00:00</t>
+          <t>31/12/2024 00:00</t>
         </is>
       </c>
       <c r="X30" s="1" t="inlineStr">
         <is>
-          <t>05/07/2024 00:00</t>
+          <t>05/12/2024 00:00</t>
         </is>
       </c>
       <c r="Y30" s="1" t="inlineStr">
         <is>
-          <t>SEPARACION</t>
+          <t>CUOTA INICIAL</t>
         </is>
       </c>
       <c r="Z30" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA30" s="1" t="inlineStr">
         <is>
-          <t>3000.00</t>
+          <t>30000.00</t>
         </is>
       </c>
       <c r="AB30" s="1" t="inlineStr">
@@ -7058,12 +7162,12 @@
       </c>
       <c r="AD30" s="1" t="inlineStr">
         <is>
-          <t>3000.00</t>
+          <t>30000.00</t>
         </is>
       </c>
       <c r="AE30" s="1" t="inlineStr">
         <is>
-          <t>3000.00</t>
+          <t>30000.00</t>
         </is>
       </c>
       <c r="AF30" s="1" t="inlineStr">
@@ -7078,7 +7182,7 @@
       </c>
       <c r="AH30" s="1" t="inlineStr">
         <is>
-          <t>Ahorro</t>
+          <t>Crédito Hipotecario</t>
         </is>
       </c>
       <c r="AI30" s="1" t="inlineStr">
@@ -7093,13 +7197,17 @@
       </c>
       <c r="AK30" s="1" t="inlineStr">
         <is>
-          <t>TRANSFERENCIA BANCARIA</t>
-        </is>
-      </c>
-      <c r="AL30" s="1" t="inlineStr"/>
+          <t>DEPOSITO EN CUENTA</t>
+        </is>
+      </c>
+      <c r="AL30" s="1" t="inlineStr">
+        <is>
+          <t>15764694</t>
+        </is>
+      </c>
       <c r="AM30" s="1" t="inlineStr">
         <is>
-          <t>0040</t>
+          <t>05000010069</t>
         </is>
       </c>
       <c r="AN30" s="1" t="inlineStr">
@@ -7107,7 +7215,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AO30" s="1" t="inlineStr"/>
+      <c r="AO30" s="1" t="inlineStr">
+        <is>
+          <t>NO PRECISA</t>
+        </is>
+      </c>
       <c r="AP30" s="1" t="inlineStr">
         <is>
           <t>1.00</t>
@@ -7130,12 +7242,12 @@
       <c r="BA30" s="1" t="inlineStr"/>
       <c r="BB30" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="BC30" s="1" t="inlineStr">
         <is>
-          <t>02/10/2024 16:40</t>
+          <t>29/10/2024 16:25</t>
         </is>
       </c>
       <c r="BD30" s="1" t="inlineStr">
@@ -7146,12 +7258,12 @@
       <c r="BE30" s="1" t="inlineStr"/>
       <c r="BF30" s="1" t="inlineStr">
         <is>
-          <t>000011</t>
+          <t>000001</t>
         </is>
       </c>
       <c r="BG30" s="1" t="inlineStr">
         <is>
-          <t>29/05/2026 12:21</t>
+          <t>29/05/2026 12:20</t>
         </is>
       </c>
     </row>
@@ -7183,7 +7295,7 @@
       </c>
       <c r="F31" s="1" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>403</t>
         </is>
       </c>
       <c r="G31" s="1" t="inlineStr">
@@ -7196,95 +7308,71 @@
           <t>654000.00</t>
         </is>
       </c>
-      <c r="I31" s="1" t="inlineStr">
-        <is>
-          <t>Edificio</t>
-        </is>
-      </c>
-      <c r="J31" s="1" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K31" s="1" t="inlineStr">
-        <is>
-          <t>Estacionamiento</t>
-        </is>
-      </c>
-      <c r="L31" s="1" t="inlineStr">
-        <is>
-          <t>E 37 - D 28</t>
-        </is>
-      </c>
-      <c r="M31" s="1" t="inlineStr">
-        <is>
-          <t>52000.00</t>
-        </is>
-      </c>
-      <c r="N31" s="1" t="inlineStr">
-        <is>
-          <t>52000.00</t>
-        </is>
-      </c>
+      <c r="I31" s="1" t="inlineStr"/>
+      <c r="J31" s="1" t="inlineStr"/>
+      <c r="K31" s="1" t="inlineStr"/>
+      <c r="L31" s="1" t="inlineStr"/>
+      <c r="M31" s="1" t="inlineStr"/>
+      <c r="N31" s="1" t="inlineStr"/>
       <c r="O31" s="1" t="inlineStr">
         <is>
-          <t>Luis Alberto Ovalle Huamanguilla</t>
+          <t>Liliana Lucila Luciano Claros</t>
         </is>
       </c>
       <c r="P31" s="1" t="inlineStr">
         <is>
-          <t>43953371</t>
+          <t>15764694</t>
         </is>
       </c>
       <c r="Q31" s="1" t="inlineStr">
         <is>
-          <t>JR. NAPO NRO. 821</t>
+          <t xml:space="preserve">MZ M5 – Lt. 7 urb. Paseo del Mar </t>
         </is>
       </c>
       <c r="R31" s="1" t="inlineStr"/>
       <c r="S31" s="1" t="inlineStr">
         <is>
-          <t>992764943</t>
+          <t>982406857</t>
         </is>
       </c>
       <c r="T31" s="1" t="inlineStr">
         <is>
-          <t>aovalle2212@gmail.com</t>
+          <t>liliana31_micaela@hotmail.com</t>
         </is>
       </c>
       <c r="U31" s="1" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>SANTA</t>
         </is>
       </c>
       <c r="V31" s="1" t="inlineStr">
         <is>
-          <t>BREÑA</t>
+          <t>NUEVO CHIMBOTE</t>
         </is>
       </c>
       <c r="W31" s="1" t="inlineStr">
         <is>
-          <t>02/10/2024 00:00</t>
+          <t>31/12/2024 00:00</t>
         </is>
       </c>
       <c r="X31" s="1" t="inlineStr">
         <is>
-          <t>02/10/2024 00:00</t>
+          <t>07/03/2025 00:00</t>
         </is>
       </c>
       <c r="Y31" s="1" t="inlineStr">
         <is>
-          <t>CUOTA INICIAL</t>
+          <t>SALDO FINANCIAR</t>
         </is>
       </c>
       <c r="Z31" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA31" s="1" t="inlineStr">
         <is>
-          <t>25000.00</t>
+          <t>523200.00</t>
         </is>
       </c>
       <c r="AB31" s="1" t="inlineStr">
@@ -7299,12 +7387,12 @@
       </c>
       <c r="AD31" s="1" t="inlineStr">
         <is>
-          <t>25000.00</t>
+          <t>523200.00</t>
         </is>
       </c>
       <c r="AE31" s="1" t="inlineStr">
         <is>
-          <t>25000.00</t>
+          <t>523200.00</t>
         </is>
       </c>
       <c r="AF31" s="1" t="inlineStr">
@@ -7319,7 +7407,7 @@
       </c>
       <c r="AH31" s="1" t="inlineStr">
         <is>
-          <t>Ahorro</t>
+          <t>Crédito Hipotecario</t>
         </is>
       </c>
       <c r="AI31" s="1" t="inlineStr">
@@ -7337,14 +7425,10 @@
           <t>TRANSFERENCIA BANCARIA</t>
         </is>
       </c>
-      <c r="AL31" s="1" t="inlineStr">
-        <is>
-          <t>43953371</t>
-        </is>
-      </c>
+      <c r="AL31" s="1" t="inlineStr"/>
       <c r="AM31" s="1" t="inlineStr">
         <is>
-          <t>06056215</t>
+          <t>07032025</t>
         </is>
       </c>
       <c r="AN31" s="1" t="inlineStr">
@@ -7352,14 +7436,10 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AO31" s="1" t="inlineStr">
-        <is>
-          <t>NO PRECISA</t>
-        </is>
-      </c>
+      <c r="AO31" s="1" t="inlineStr"/>
       <c r="AP31" s="1" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="AQ31" s="1" t="inlineStr">
@@ -7384,7 +7464,7 @@
       </c>
       <c r="BC31" s="1" t="inlineStr">
         <is>
-          <t>02/10/2024 16:40</t>
+          <t>29/10/2024 16:25</t>
         </is>
       </c>
       <c r="BD31" s="1" t="inlineStr">
@@ -7395,12 +7475,12 @@
       <c r="BE31" s="1" t="inlineStr"/>
       <c r="BF31" s="1" t="inlineStr">
         <is>
-          <t>000011</t>
+          <t>000001</t>
         </is>
       </c>
       <c r="BG31" s="1" t="inlineStr">
         <is>
-          <t>29/05/2026 12:21</t>
+          <t>07/07/2026 09:31</t>
         </is>
       </c>
     </row>
@@ -7432,17 +7512,17 @@
       </c>
       <c r="F32" s="1" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>603</t>
         </is>
       </c>
       <c r="G32" s="1" t="inlineStr">
         <is>
-          <t>446900.00</t>
+          <t>654000.00</t>
         </is>
       </c>
       <c r="H32" s="1" t="inlineStr">
         <is>
-          <t>446900.00</t>
+          <t>654000.00</t>
         </is>
       </c>
       <c r="I32" s="1" t="inlineStr"/>
@@ -7453,52 +7533,48 @@
       <c r="N32" s="1" t="inlineStr"/>
       <c r="O32" s="1" t="inlineStr">
         <is>
-          <t>María Cristina Collazos Romero</t>
+          <t>Luis Alberto Ovalle Huamanguilla</t>
         </is>
       </c>
       <c r="P32" s="1" t="inlineStr">
         <is>
-          <t>31676885</t>
+          <t>43953371</t>
         </is>
       </c>
       <c r="Q32" s="1" t="inlineStr">
         <is>
-          <t>Jr. Huandoy 242</t>
-        </is>
-      </c>
-      <c r="R32" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">969870030 </t>
-        </is>
-      </c>
+          <t>JR. NAPO NRO. 821</t>
+        </is>
+      </c>
+      <c r="R32" s="1" t="inlineStr"/>
       <c r="S32" s="1" t="inlineStr">
         <is>
-          <t>969870030</t>
+          <t>992764943</t>
         </is>
       </c>
       <c r="T32" s="1" t="inlineStr">
         <is>
-          <t>gerenciasnacks1@gmail.com</t>
+          <t>aovalle2212@gmail.com</t>
         </is>
       </c>
       <c r="U32" s="1" t="inlineStr">
         <is>
-          <t>HUARAZ</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="V32" s="1" t="inlineStr">
         <is>
-          <t>HUARAZ</t>
+          <t>BREÑA</t>
         </is>
       </c>
       <c r="W32" s="1" t="inlineStr">
         <is>
-          <t>22/08/2024 00:00</t>
+          <t>04/07/2024 00:00</t>
         </is>
       </c>
       <c r="X32" s="1" t="inlineStr">
         <is>
-          <t>22/08/2024 00:00</t>
+          <t>04/07/2024 00:00</t>
         </is>
       </c>
       <c r="Y32" s="1" t="inlineStr">
@@ -7548,7 +7624,7 @@
       </c>
       <c r="AH32" s="1" t="inlineStr">
         <is>
-          <t>Crédito Hipotecario</t>
+          <t>Ahorro</t>
         </is>
       </c>
       <c r="AI32" s="1" t="inlineStr">
@@ -7566,14 +7642,10 @@
           <t>TRANSFERENCIA BANCARIA</t>
         </is>
       </c>
-      <c r="AL32" s="1" t="inlineStr">
-        <is>
-          <t>31676885</t>
-        </is>
-      </c>
+      <c r="AL32" s="1" t="inlineStr"/>
       <c r="AM32" s="1" t="inlineStr">
         <is>
-          <t>0500010101</t>
+          <t>901866</t>
         </is>
       </c>
       <c r="AN32" s="1" t="inlineStr">
@@ -7581,11 +7653,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AO32" s="1" t="inlineStr">
-        <is>
-          <t>NO PRECISA</t>
-        </is>
-      </c>
+      <c r="AO32" s="1" t="inlineStr"/>
       <c r="AP32" s="1" t="inlineStr">
         <is>
           <t>4.00</t>
@@ -7613,23 +7681,23 @@
       </c>
       <c r="BC32" s="1" t="inlineStr">
         <is>
-          <t>11/09/2025 14:34</t>
+          <t>02/10/2024 16:40</t>
         </is>
       </c>
       <c r="BD32" s="1" t="inlineStr">
         <is>
-          <t>Kenny Salazar S</t>
+          <t>Carla Michue M</t>
         </is>
       </c>
       <c r="BE32" s="1" t="inlineStr"/>
       <c r="BF32" s="1" t="inlineStr">
         <is>
-          <t>000033</t>
+          <t>000011</t>
         </is>
       </c>
       <c r="BG32" s="1" t="inlineStr">
         <is>
-          <t>02/06/2026 15:10</t>
+          <t>07/07/2026 10:58</t>
         </is>
       </c>
     </row>
@@ -7661,17 +7729,17 @@
       </c>
       <c r="F33" s="1" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>603</t>
         </is>
       </c>
       <c r="G33" s="1" t="inlineStr">
         <is>
-          <t>490000.00</t>
+          <t>654000.00</t>
         </is>
       </c>
       <c r="H33" s="1" t="inlineStr">
         <is>
-          <t>490000.00</t>
+          <t>654000.00</t>
         </is>
       </c>
       <c r="I33" s="1" t="inlineStr"/>
@@ -7682,32 +7750,28 @@
       <c r="N33" s="1" t="inlineStr"/>
       <c r="O33" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marina Francisca Vasquez Samaniego </t>
+          <t>Luis Alberto Ovalle Huamanguilla</t>
         </is>
       </c>
       <c r="P33" s="1" t="inlineStr">
         <is>
-          <t>19907001</t>
+          <t>43953371</t>
         </is>
       </c>
       <c r="Q33" s="1" t="inlineStr">
         <is>
-          <t>Huandoy 887</t>
-        </is>
-      </c>
-      <c r="R33" s="1" t="inlineStr">
-        <is>
-          <t>964247615</t>
-        </is>
-      </c>
+          <t>JR. NAPO NRO. 821</t>
+        </is>
+      </c>
+      <c r="R33" s="1" t="inlineStr"/>
       <c r="S33" s="1" t="inlineStr">
         <is>
-          <t>964247615</t>
+          <t>992764943</t>
         </is>
       </c>
       <c r="T33" s="1" t="inlineStr">
         <is>
-          <t>francisca4547@hotmail.com</t>
+          <t>aovalle2212@gmail.com</t>
         </is>
       </c>
       <c r="U33" s="1" t="inlineStr">
@@ -7717,22 +7781,22 @@
       </c>
       <c r="V33" s="1" t="inlineStr">
         <is>
-          <t>SAN MIGUEL</t>
+          <t>BREÑA</t>
         </is>
       </c>
       <c r="W33" s="1" t="inlineStr">
         <is>
-          <t>21/11/2024 00:00</t>
+          <t>31/12/2024 00:00</t>
         </is>
       </c>
       <c r="X33" s="1" t="inlineStr">
         <is>
-          <t>21/11/2024 00:00</t>
+          <t>02/10/2024 00:00</t>
         </is>
       </c>
       <c r="Y33" s="1" t="inlineStr">
         <is>
-          <t>SEPARACION</t>
+          <t>CUOTA INICIAL</t>
         </is>
       </c>
       <c r="Z33" s="1" t="inlineStr">
@@ -7742,7 +7806,7 @@
       </c>
       <c r="AA33" s="1" t="inlineStr">
         <is>
-          <t>3000.00</t>
+          <t>57400.00</t>
         </is>
       </c>
       <c r="AB33" s="1" t="inlineStr">
@@ -7757,12 +7821,12 @@
       </c>
       <c r="AD33" s="1" t="inlineStr">
         <is>
-          <t>3000.00</t>
+          <t>57400.00</t>
         </is>
       </c>
       <c r="AE33" s="1" t="inlineStr">
         <is>
-          <t>3000.00</t>
+          <t>20000.00</t>
         </is>
       </c>
       <c r="AF33" s="1" t="inlineStr">
@@ -7777,7 +7841,7 @@
       </c>
       <c r="AH33" s="1" t="inlineStr">
         <is>
-          <t>Crédito Hipotecario</t>
+          <t>Ahorro</t>
         </is>
       </c>
       <c r="AI33" s="1" t="inlineStr">
@@ -7795,14 +7859,10 @@
           <t>TRANSFERENCIA BANCARIA</t>
         </is>
       </c>
-      <c r="AL33" s="1" t="inlineStr">
-        <is>
-          <t>19907001</t>
-        </is>
-      </c>
+      <c r="AL33" s="1" t="inlineStr"/>
       <c r="AM33" s="1" t="inlineStr">
         <is>
-          <t>00951165</t>
+          <t>06056215</t>
         </is>
       </c>
       <c r="AN33" s="1" t="inlineStr">
@@ -7810,11 +7870,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AO33" s="1" t="inlineStr">
-        <is>
-          <t>NO PRECISA</t>
-        </is>
-      </c>
+      <c r="AO33" s="1" t="inlineStr"/>
       <c r="AP33" s="1" t="inlineStr">
         <is>
           <t>4.00</t>
@@ -7842,23 +7898,23 @@
       </c>
       <c r="BC33" s="1" t="inlineStr">
         <is>
-          <t>26/12/2024 14:48</t>
+          <t>02/10/2024 16:40</t>
         </is>
       </c>
       <c r="BD33" s="1" t="inlineStr">
         <is>
-          <t>Kenny Salazar S</t>
+          <t>Carla Michue M</t>
         </is>
       </c>
       <c r="BE33" s="1" t="inlineStr"/>
       <c r="BF33" s="1" t="inlineStr">
         <is>
-          <t>000037</t>
+          <t>000011</t>
         </is>
       </c>
       <c r="BG33" s="1" t="inlineStr">
         <is>
-          <t>02/06/2026 17:25</t>
+          <t>07/07/2026 11:03</t>
         </is>
       </c>
     </row>
@@ -7890,17 +7946,17 @@
       </c>
       <c r="F34" s="1" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>603</t>
         </is>
       </c>
       <c r="G34" s="1" t="inlineStr">
         <is>
-          <t>490000.00</t>
+          <t>654000.00</t>
         </is>
       </c>
       <c r="H34" s="1" t="inlineStr">
         <is>
-          <t>490000.00</t>
+          <t>654000.00</t>
         </is>
       </c>
       <c r="I34" s="1" t="inlineStr"/>
@@ -7911,32 +7967,28 @@
       <c r="N34" s="1" t="inlineStr"/>
       <c r="O34" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marina Francisca Vasquez Samaniego </t>
+          <t>Luis Alberto Ovalle Huamanguilla</t>
         </is>
       </c>
       <c r="P34" s="1" t="inlineStr">
         <is>
-          <t>19907001</t>
+          <t>43953371</t>
         </is>
       </c>
       <c r="Q34" s="1" t="inlineStr">
         <is>
-          <t>Huandoy 887</t>
-        </is>
-      </c>
-      <c r="R34" s="1" t="inlineStr">
-        <is>
-          <t>964247615</t>
-        </is>
-      </c>
+          <t>JR. NAPO NRO. 821</t>
+        </is>
+      </c>
+      <c r="R34" s="1" t="inlineStr"/>
       <c r="S34" s="1" t="inlineStr">
         <is>
-          <t>964247615</t>
+          <t>992764943</t>
         </is>
       </c>
       <c r="T34" s="1" t="inlineStr">
         <is>
-          <t>francisca4547@hotmail.com</t>
+          <t>aovalle2212@gmail.com</t>
         </is>
       </c>
       <c r="U34" s="1" t="inlineStr">
@@ -7946,15 +7998,19 @@
       </c>
       <c r="V34" s="1" t="inlineStr">
         <is>
-          <t>SAN MIGUEL</t>
+          <t>BREÑA</t>
         </is>
       </c>
       <c r="W34" s="1" t="inlineStr">
         <is>
-          <t>26/12/2024 00:00</t>
-        </is>
-      </c>
-      <c r="X34" s="1" t="inlineStr"/>
+          <t>31/12/2024 00:00</t>
+        </is>
+      </c>
+      <c r="X34" s="1" t="inlineStr">
+        <is>
+          <t>07/03/2025 00:00</t>
+        </is>
+      </c>
       <c r="Y34" s="1" t="inlineStr">
         <is>
           <t>CUOTA INICIAL</t>
@@ -7967,7 +8023,7 @@
       </c>
       <c r="AA34" s="1" t="inlineStr">
         <is>
-          <t>20000.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB34" s="1" t="inlineStr">
@@ -7982,40 +8038,64 @@
       </c>
       <c r="AD34" s="1" t="inlineStr">
         <is>
-          <t>20000.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AE34" s="1" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>37400.00</t>
         </is>
       </c>
       <c r="AF34" s="1" t="inlineStr">
         <is>
-          <t>20000.00</t>
-        </is>
-      </c>
-      <c r="AG34" s="1" t="inlineStr"/>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AG34" s="1" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
       <c r="AH34" s="1" t="inlineStr">
         <is>
-          <t>Crédito Hipotecario</t>
-        </is>
-      </c>
-      <c r="AI34" s="1" t="inlineStr"/>
-      <c r="AJ34" s="1" t="inlineStr"/>
-      <c r="AK34" s="1" t="inlineStr"/>
+          <t>Ahorro</t>
+        </is>
+      </c>
+      <c r="AI34" s="1" t="inlineStr">
+        <is>
+          <t>Scotiabank Perú</t>
+        </is>
+      </c>
+      <c r="AJ34" s="1" t="inlineStr">
+        <is>
+          <t>000-2768484</t>
+        </is>
+      </c>
+      <c r="AK34" s="1" t="inlineStr">
+        <is>
+          <t>TRANSFERENCIA BANCARIA</t>
+        </is>
+      </c>
       <c r="AL34" s="1" t="inlineStr"/>
-      <c r="AM34" s="1" t="inlineStr"/>
+      <c r="AM34" s="1" t="inlineStr">
+        <is>
+          <t>U26926</t>
+        </is>
+      </c>
       <c r="AN34" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
       <c r="AO34" s="1" t="inlineStr"/>
-      <c r="AP34" s="1" t="inlineStr"/>
+      <c r="AP34" s="1" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
       <c r="AQ34" s="1" t="inlineStr">
         <is>
-          <t>VENCIDO</t>
+          <t>CANCELADO</t>
         </is>
       </c>
       <c r="AR34" s="1" t="inlineStr"/>
@@ -8030,26 +8110,30 @@
       <c r="BA34" s="1" t="inlineStr"/>
       <c r="BB34" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="BC34" s="1" t="inlineStr">
         <is>
-          <t>26/12/2024 14:48</t>
+          <t>02/10/2024 16:40</t>
         </is>
       </c>
       <c r="BD34" s="1" t="inlineStr">
         <is>
-          <t>Kenny Salazar S</t>
+          <t>Carla Michue M</t>
         </is>
       </c>
       <c r="BE34" s="1" t="inlineStr"/>
       <c r="BF34" s="1" t="inlineStr">
         <is>
-          <t>000037</t>
-        </is>
-      </c>
-      <c r="BG34" s="1" t="inlineStr"/>
+          <t>000011</t>
+        </is>
+      </c>
+      <c r="BG34" s="1" t="inlineStr">
+        <is>
+          <t>07/07/2026 11:04</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
@@ -8079,17 +8163,17 @@
       </c>
       <c r="F35" s="1" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>202</t>
         </is>
       </c>
       <c r="G35" s="1" t="inlineStr">
         <is>
-          <t>592500.00</t>
+          <t>446900.00</t>
         </is>
       </c>
       <c r="H35" s="1" t="inlineStr">
         <is>
-          <t>592500.00</t>
+          <t>446900.00</t>
         </is>
       </c>
       <c r="I35" s="1" t="inlineStr"/>
@@ -8100,48 +8184,52 @@
       <c r="N35" s="1" t="inlineStr"/>
       <c r="O35" s="1" t="inlineStr">
         <is>
-          <t>Richard Humberto Lima Garcia</t>
+          <t>María Cristina Collazos Romero</t>
         </is>
       </c>
       <c r="P35" s="1" t="inlineStr">
         <is>
-          <t>10606793</t>
+          <t>31676885</t>
         </is>
       </c>
       <c r="Q35" s="1" t="inlineStr">
         <is>
-          <t>Mz E2 lote 10 Urb Coovitiomar - Ancón</t>
-        </is>
-      </c>
-      <c r="R35" s="1" t="inlineStr"/>
+          <t>Jr. Huandoy 242</t>
+        </is>
+      </c>
+      <c r="R35" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">969870030 </t>
+        </is>
+      </c>
       <c r="S35" s="1" t="inlineStr">
         <is>
-          <t>940170759</t>
+          <t>969870030</t>
         </is>
       </c>
       <c r="T35" s="1" t="inlineStr">
         <is>
-          <t>richard_13_312@hotmail.com</t>
+          <t>gerenciasnacks1@gmail.com</t>
         </is>
       </c>
       <c r="U35" s="1" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>HUARAZ</t>
         </is>
       </c>
       <c r="V35" s="1" t="inlineStr">
         <is>
-          <t>SANTA ROSA</t>
+          <t>HUARAZ</t>
         </is>
       </c>
       <c r="W35" s="1" t="inlineStr">
         <is>
-          <t>28/10/2024 00:00</t>
+          <t>22/08/2024 00:00</t>
         </is>
       </c>
       <c r="X35" s="1" t="inlineStr">
         <is>
-          <t>28/10/2024 00:00</t>
+          <t>22/08/2024 00:00</t>
         </is>
       </c>
       <c r="Y35" s="1" t="inlineStr">
@@ -8211,12 +8299,12 @@
       </c>
       <c r="AL35" s="1" t="inlineStr">
         <is>
-          <t>10606793</t>
+          <t>31676885</t>
         </is>
       </c>
       <c r="AM35" s="1" t="inlineStr">
         <is>
-          <t>01525977</t>
+          <t>0500010101</t>
         </is>
       </c>
       <c r="AN35" s="1" t="inlineStr">
@@ -8231,7 +8319,7 @@
       </c>
       <c r="AP35" s="1" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="AQ35" s="1" t="inlineStr">
@@ -8256,23 +8344,23 @@
       </c>
       <c r="BC35" s="1" t="inlineStr">
         <is>
-          <t>12/12/2024 16:44</t>
+          <t>11/09/2025 14:34</t>
         </is>
       </c>
       <c r="BD35" s="1" t="inlineStr">
         <is>
-          <t>Carla Michue M</t>
+          <t>Kenny Salazar S</t>
         </is>
       </c>
       <c r="BE35" s="1" t="inlineStr"/>
       <c r="BF35" s="1" t="inlineStr">
         <is>
-          <t>000003</t>
+          <t>000033</t>
         </is>
       </c>
       <c r="BG35" s="1" t="inlineStr">
         <is>
-          <t>29/05/2026 12:21</t>
+          <t>02/06/2026 15:10</t>
         </is>
       </c>
     </row>
@@ -8304,17 +8392,17 @@
       </c>
       <c r="F36" s="1" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>505</t>
         </is>
       </c>
       <c r="G36" s="1" t="inlineStr">
         <is>
-          <t>592500.00</t>
+          <t>490000.00</t>
         </is>
       </c>
       <c r="H36" s="1" t="inlineStr">
         <is>
-          <t>592500.00</t>
+          <t>490000.00</t>
         </is>
       </c>
       <c r="I36" s="1" t="inlineStr"/>
@@ -8325,28 +8413,32 @@
       <c r="N36" s="1" t="inlineStr"/>
       <c r="O36" s="1" t="inlineStr">
         <is>
-          <t>Richard Humberto Lima Garcia</t>
+          <t xml:space="preserve">Marina Francisca Vasquez Samaniego </t>
         </is>
       </c>
       <c r="P36" s="1" t="inlineStr">
         <is>
-          <t>10606793</t>
+          <t>19907001</t>
         </is>
       </c>
       <c r="Q36" s="1" t="inlineStr">
         <is>
-          <t>Mz E2 lote 10 Urb Coovitiomar - Ancón</t>
-        </is>
-      </c>
-      <c r="R36" s="1" t="inlineStr"/>
+          <t>Huandoy 887</t>
+        </is>
+      </c>
+      <c r="R36" s="1" t="inlineStr">
+        <is>
+          <t>964247615</t>
+        </is>
+      </c>
       <c r="S36" s="1" t="inlineStr">
         <is>
-          <t>940170759</t>
+          <t>964247615</t>
         </is>
       </c>
       <c r="T36" s="1" t="inlineStr">
         <is>
-          <t>richard_13_312@hotmail.com</t>
+          <t>francisca4547@hotmail.com</t>
         </is>
       </c>
       <c r="U36" s="1" t="inlineStr">
@@ -8356,32 +8448,32 @@
       </c>
       <c r="V36" s="1" t="inlineStr">
         <is>
-          <t>SANTA ROSA</t>
+          <t>SAN MIGUEL</t>
         </is>
       </c>
       <c r="W36" s="1" t="inlineStr">
         <is>
-          <t>22/11/2024 00:00</t>
+          <t>21/11/2024 00:00</t>
         </is>
       </c>
       <c r="X36" s="1" t="inlineStr">
         <is>
-          <t>26/11/2024 00:00</t>
+          <t>21/11/2024 00:00</t>
         </is>
       </c>
       <c r="Y36" s="1" t="inlineStr">
         <is>
-          <t>CUOTA INICIAL</t>
+          <t>SEPARACION</t>
         </is>
       </c>
       <c r="Z36" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA36" s="1" t="inlineStr">
         <is>
-          <t>48000.00</t>
+          <t>3000.00</t>
         </is>
       </c>
       <c r="AB36" s="1" t="inlineStr">
@@ -8396,12 +8488,12 @@
       </c>
       <c r="AD36" s="1" t="inlineStr">
         <is>
-          <t>48000.00</t>
+          <t>3000.00</t>
         </is>
       </c>
       <c r="AE36" s="1" t="inlineStr">
         <is>
-          <t>48000.00</t>
+          <t>3000.00</t>
         </is>
       </c>
       <c r="AF36" s="1" t="inlineStr">
@@ -8436,12 +8528,12 @@
       </c>
       <c r="AL36" s="1" t="inlineStr">
         <is>
-          <t>10606793</t>
+          <t>19907001</t>
         </is>
       </c>
       <c r="AM36" s="1" t="inlineStr">
         <is>
-          <t>0144739</t>
+          <t>00951165</t>
         </is>
       </c>
       <c r="AN36" s="1" t="inlineStr">
@@ -8456,7 +8548,7 @@
       </c>
       <c r="AP36" s="1" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="AQ36" s="1" t="inlineStr">
@@ -8481,23 +8573,23 @@
       </c>
       <c r="BC36" s="1" t="inlineStr">
         <is>
-          <t>12/12/2024 16:44</t>
+          <t>26/12/2024 14:48</t>
         </is>
       </c>
       <c r="BD36" s="1" t="inlineStr">
         <is>
-          <t>Carla Michue M</t>
+          <t>Kenny Salazar S</t>
         </is>
       </c>
       <c r="BE36" s="1" t="inlineStr"/>
       <c r="BF36" s="1" t="inlineStr">
         <is>
-          <t>000003</t>
+          <t>000037</t>
         </is>
       </c>
       <c r="BG36" s="1" t="inlineStr">
         <is>
-          <t>29/05/2026 12:21</t>
+          <t>02/06/2026 17:25</t>
         </is>
       </c>
     </row>
@@ -8529,17 +8621,17 @@
       </c>
       <c r="F37" s="1" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>505</t>
         </is>
       </c>
       <c r="G37" s="1" t="inlineStr">
         <is>
-          <t>592500.00</t>
+          <t>490000.00</t>
         </is>
       </c>
       <c r="H37" s="1" t="inlineStr">
         <is>
-          <t>592500.00</t>
+          <t>490000.00</t>
         </is>
       </c>
       <c r="I37" s="1" t="inlineStr"/>
@@ -8550,28 +8642,32 @@
       <c r="N37" s="1" t="inlineStr"/>
       <c r="O37" s="1" t="inlineStr">
         <is>
-          <t>Richard Humberto Lima Garcia</t>
+          <t xml:space="preserve">Marina Francisca Vasquez Samaniego </t>
         </is>
       </c>
       <c r="P37" s="1" t="inlineStr">
         <is>
-          <t>10606793</t>
+          <t>19907001</t>
         </is>
       </c>
       <c r="Q37" s="1" t="inlineStr">
         <is>
-          <t>Mz E2 lote 10 Urb Coovitiomar - Ancón</t>
-        </is>
-      </c>
-      <c r="R37" s="1" t="inlineStr"/>
+          <t>Huandoy 887</t>
+        </is>
+      </c>
+      <c r="R37" s="1" t="inlineStr">
+        <is>
+          <t>964247615</t>
+        </is>
+      </c>
       <c r="S37" s="1" t="inlineStr">
         <is>
-          <t>940170759</t>
+          <t>964247615</t>
         </is>
       </c>
       <c r="T37" s="1" t="inlineStr">
         <is>
-          <t>richard_13_312@hotmail.com</t>
+          <t>francisca4547@hotmail.com</t>
         </is>
       </c>
       <c r="U37" s="1" t="inlineStr">
@@ -8581,17 +8677,17 @@
       </c>
       <c r="V37" s="1" t="inlineStr">
         <is>
-          <t>SANTA ROSA</t>
+          <t>SAN MIGUEL</t>
         </is>
       </c>
       <c r="W37" s="1" t="inlineStr">
         <is>
-          <t>12/12/2024 00:00</t>
+          <t>26/12/2024 00:00</t>
         </is>
       </c>
       <c r="X37" s="1" t="inlineStr">
         <is>
-          <t>12/12/2024 00:00</t>
+          <t>26/12/2024 00:00</t>
         </is>
       </c>
       <c r="Y37" s="1" t="inlineStr">
@@ -8601,12 +8697,12 @@
       </c>
       <c r="Z37" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA37" s="1" t="inlineStr">
         <is>
-          <t>8250.00</t>
+          <t>20000.00</t>
         </is>
       </c>
       <c r="AB37" s="1" t="inlineStr">
@@ -8621,12 +8717,12 @@
       </c>
       <c r="AD37" s="1" t="inlineStr">
         <is>
-          <t>8250.00</t>
+          <t>20000.00</t>
         </is>
       </c>
       <c r="AE37" s="1" t="inlineStr">
         <is>
-          <t>8250.00</t>
+          <t>20000.00</t>
         </is>
       </c>
       <c r="AF37" s="1" t="inlineStr">
@@ -8659,14 +8755,10 @@
           <t>TRANSFERENCIA BANCARIA</t>
         </is>
       </c>
-      <c r="AL37" s="1" t="inlineStr">
-        <is>
-          <t>10606793</t>
-        </is>
-      </c>
+      <c r="AL37" s="1" t="inlineStr"/>
       <c r="AM37" s="1" t="inlineStr">
         <is>
-          <t>02209753</t>
+          <t>6204304</t>
         </is>
       </c>
       <c r="AN37" s="1" t="inlineStr">
@@ -8674,14 +8766,10 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AO37" s="1" t="inlineStr">
-        <is>
-          <t>NO PRECISA</t>
-        </is>
-      </c>
+      <c r="AO37" s="1" t="inlineStr"/>
       <c r="AP37" s="1" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="AQ37" s="1" t="inlineStr">
@@ -8706,23 +8794,23 @@
       </c>
       <c r="BC37" s="1" t="inlineStr">
         <is>
-          <t>12/12/2024 16:44</t>
+          <t>26/12/2024 14:48</t>
         </is>
       </c>
       <c r="BD37" s="1" t="inlineStr">
         <is>
-          <t>Carla Michue M</t>
+          <t>Kenny Salazar S</t>
         </is>
       </c>
       <c r="BE37" s="1" t="inlineStr"/>
       <c r="BF37" s="1" t="inlineStr">
         <is>
-          <t>000003</t>
+          <t>000037</t>
         </is>
       </c>
       <c r="BG37" s="1" t="inlineStr">
         <is>
-          <t>29/05/2026 12:21</t>
+          <t>07/07/2026 10:35</t>
         </is>
       </c>
     </row>
@@ -8811,23 +8899,27 @@
       </c>
       <c r="W38" s="1" t="inlineStr">
         <is>
-          <t>31/12/2024 00:00</t>
-        </is>
-      </c>
-      <c r="X38" s="1" t="inlineStr"/>
+          <t>28/10/2024 00:00</t>
+        </is>
+      </c>
+      <c r="X38" s="1" t="inlineStr">
+        <is>
+          <t>28/10/2024 00:00</t>
+        </is>
+      </c>
       <c r="Y38" s="1" t="inlineStr">
         <is>
-          <t>SALDO FINANCIAR</t>
+          <t>SEPARACION</t>
         </is>
       </c>
       <c r="Z38" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA38" s="1" t="inlineStr">
         <is>
-          <t>533250.00</t>
+          <t>3000.00</t>
         </is>
       </c>
       <c r="AB38" s="1" t="inlineStr">
@@ -8842,40 +8934,72 @@
       </c>
       <c r="AD38" s="1" t="inlineStr">
         <is>
-          <t>533250.00</t>
+          <t>3000.00</t>
         </is>
       </c>
       <c r="AE38" s="1" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3000.00</t>
         </is>
       </c>
       <c r="AF38" s="1" t="inlineStr">
         <is>
-          <t>533250.00</t>
-        </is>
-      </c>
-      <c r="AG38" s="1" t="inlineStr"/>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AG38" s="1" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
       <c r="AH38" s="1" t="inlineStr">
         <is>
           <t>Crédito Hipotecario</t>
         </is>
       </c>
-      <c r="AI38" s="1" t="inlineStr"/>
-      <c r="AJ38" s="1" t="inlineStr"/>
-      <c r="AK38" s="1" t="inlineStr"/>
-      <c r="AL38" s="1" t="inlineStr"/>
-      <c r="AM38" s="1" t="inlineStr"/>
+      <c r="AI38" s="1" t="inlineStr">
+        <is>
+          <t>Scotiabank Perú</t>
+        </is>
+      </c>
+      <c r="AJ38" s="1" t="inlineStr">
+        <is>
+          <t>000-2768484</t>
+        </is>
+      </c>
+      <c r="AK38" s="1" t="inlineStr">
+        <is>
+          <t>TRANSFERENCIA BANCARIA</t>
+        </is>
+      </c>
+      <c r="AL38" s="1" t="inlineStr">
+        <is>
+          <t>10606793</t>
+        </is>
+      </c>
+      <c r="AM38" s="1" t="inlineStr">
+        <is>
+          <t>01525977</t>
+        </is>
+      </c>
       <c r="AN38" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AO38" s="1" t="inlineStr"/>
-      <c r="AP38" s="1" t="inlineStr"/>
+      <c r="AO38" s="1" t="inlineStr">
+        <is>
+          <t>NO PRECISA</t>
+        </is>
+      </c>
+      <c r="AP38" s="1" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
       <c r="AQ38" s="1" t="inlineStr">
         <is>
-          <t>VENCIDO</t>
+          <t>CANCELADO</t>
         </is>
       </c>
       <c r="AR38" s="1" t="inlineStr"/>
@@ -8890,7 +9014,7 @@
       <c r="BA38" s="1" t="inlineStr"/>
       <c r="BB38" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="BC38" s="1" t="inlineStr">
@@ -8909,7 +9033,11 @@
           <t>000003</t>
         </is>
       </c>
-      <c r="BG38" s="1" t="inlineStr"/>
+      <c r="BG38" s="1" t="inlineStr">
+        <is>
+          <t>29/05/2026 12:21</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
@@ -8939,17 +9067,17 @@
       </c>
       <c r="F39" s="1" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>701</t>
         </is>
       </c>
       <c r="G39" s="1" t="inlineStr">
         <is>
-          <t>496000.00</t>
+          <t>592500.00</t>
         </is>
       </c>
       <c r="H39" s="1" t="inlineStr">
         <is>
-          <t>496000.00</t>
+          <t>592500.00</t>
         </is>
       </c>
       <c r="I39" s="1" t="inlineStr"/>
@@ -8960,28 +9088,28 @@
       <c r="N39" s="1" t="inlineStr"/>
       <c r="O39" s="1" t="inlineStr">
         <is>
-          <t>Sthefany Carolina Rodriguez Huamán</t>
+          <t>Richard Humberto Lima Garcia</t>
         </is>
       </c>
       <c r="P39" s="1" t="inlineStr">
         <is>
-          <t>70270427</t>
+          <t>10606793</t>
         </is>
       </c>
       <c r="Q39" s="1" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Mz E2 lote 10 Urb Coovitiomar - Ancón</t>
         </is>
       </c>
       <c r="R39" s="1" t="inlineStr"/>
       <c r="S39" s="1" t="inlineStr">
         <is>
-          <t>989492681</t>
+          <t>940170759</t>
         </is>
       </c>
       <c r="T39" s="1" t="inlineStr">
         <is>
-          <t>sthefany.rodriguez2207@gmail.com</t>
+          <t>richard_13_312@hotmail.com</t>
         </is>
       </c>
       <c r="U39" s="1" t="inlineStr">
@@ -8991,32 +9119,32 @@
       </c>
       <c r="V39" s="1" t="inlineStr">
         <is>
-          <t>CERCADO DE LIMA</t>
+          <t>SANTA ROSA</t>
         </is>
       </c>
       <c r="W39" s="1" t="inlineStr">
         <is>
-          <t>21/10/2024 00:00</t>
+          <t>22/11/2024 00:00</t>
         </is>
       </c>
       <c r="X39" s="1" t="inlineStr">
         <is>
-          <t>21/10/2024 00:00</t>
+          <t>26/11/2024 00:00</t>
         </is>
       </c>
       <c r="Y39" s="1" t="inlineStr">
         <is>
-          <t>SEPARACION</t>
+          <t>CUOTA INICIAL</t>
         </is>
       </c>
       <c r="Z39" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA39" s="1" t="inlineStr">
         <is>
-          <t>200.00</t>
+          <t>48000.00</t>
         </is>
       </c>
       <c r="AB39" s="1" t="inlineStr">
@@ -9031,12 +9159,12 @@
       </c>
       <c r="AD39" s="1" t="inlineStr">
         <is>
-          <t>200.00</t>
+          <t>48000.00</t>
         </is>
       </c>
       <c r="AE39" s="1" t="inlineStr">
         <is>
-          <t>200.00</t>
+          <t>48000.00</t>
         </is>
       </c>
       <c r="AF39" s="1" t="inlineStr">
@@ -9051,7 +9179,7 @@
       </c>
       <c r="AH39" s="1" t="inlineStr">
         <is>
-          <t>Ahorro</t>
+          <t>Crédito Hipotecario</t>
         </is>
       </c>
       <c r="AI39" s="1" t="inlineStr">
@@ -9071,12 +9199,12 @@
       </c>
       <c r="AL39" s="1" t="inlineStr">
         <is>
-          <t>70270427</t>
+          <t>10606793</t>
         </is>
       </c>
       <c r="AM39" s="1" t="inlineStr">
         <is>
-          <t>7844655610334</t>
+          <t>0144739</t>
         </is>
       </c>
       <c r="AN39" s="1" t="inlineStr">
@@ -9116,7 +9244,7 @@
       </c>
       <c r="BC39" s="1" t="inlineStr">
         <is>
-          <t>21/06/2025 16:52</t>
+          <t>12/12/2024 16:44</t>
         </is>
       </c>
       <c r="BD39" s="1" t="inlineStr">
@@ -9127,12 +9255,12 @@
       <c r="BE39" s="1" t="inlineStr"/>
       <c r="BF39" s="1" t="inlineStr">
         <is>
-          <t>000002</t>
+          <t>000003</t>
         </is>
       </c>
       <c r="BG39" s="1" t="inlineStr">
         <is>
-          <t>29/05/2026 12:20</t>
+          <t>29/05/2026 12:21</t>
         </is>
       </c>
     </row>
@@ -9164,17 +9292,17 @@
       </c>
       <c r="F40" s="1" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>701</t>
         </is>
       </c>
       <c r="G40" s="1" t="inlineStr">
         <is>
-          <t>496000.00</t>
+          <t>592500.00</t>
         </is>
       </c>
       <c r="H40" s="1" t="inlineStr">
         <is>
-          <t>496000.00</t>
+          <t>592500.00</t>
         </is>
       </c>
       <c r="I40" s="1" t="inlineStr"/>
@@ -9185,28 +9313,28 @@
       <c r="N40" s="1" t="inlineStr"/>
       <c r="O40" s="1" t="inlineStr">
         <is>
-          <t>Sthefany Carolina Rodriguez Huamán</t>
+          <t>Richard Humberto Lima Garcia</t>
         </is>
       </c>
       <c r="P40" s="1" t="inlineStr">
         <is>
-          <t>70270427</t>
+          <t>10606793</t>
         </is>
       </c>
       <c r="Q40" s="1" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Mz E2 lote 10 Urb Coovitiomar - Ancón</t>
         </is>
       </c>
       <c r="R40" s="1" t="inlineStr"/>
       <c r="S40" s="1" t="inlineStr">
         <is>
-          <t>989492681</t>
+          <t>940170759</t>
         </is>
       </c>
       <c r="T40" s="1" t="inlineStr">
         <is>
-          <t>sthefany.rodriguez2207@gmail.com</t>
+          <t>richard_13_312@hotmail.com</t>
         </is>
       </c>
       <c r="U40" s="1" t="inlineStr">
@@ -9216,32 +9344,32 @@
       </c>
       <c r="V40" s="1" t="inlineStr">
         <is>
-          <t>CERCADO DE LIMA</t>
+          <t>SANTA ROSA</t>
         </is>
       </c>
       <c r="W40" s="1" t="inlineStr">
         <is>
-          <t>22/10/2024 00:00</t>
+          <t>12/12/2024 00:00</t>
         </is>
       </c>
       <c r="X40" s="1" t="inlineStr">
         <is>
-          <t>22/10/2024 00:00</t>
+          <t>12/12/2024 00:00</t>
         </is>
       </c>
       <c r="Y40" s="1" t="inlineStr">
         <is>
-          <t>SEPARACION</t>
+          <t>CUOTA INICIAL</t>
         </is>
       </c>
       <c r="Z40" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA40" s="1" t="inlineStr">
         <is>
-          <t>2800.00</t>
+          <t>8250.00</t>
         </is>
       </c>
       <c r="AB40" s="1" t="inlineStr">
@@ -9256,12 +9384,12 @@
       </c>
       <c r="AD40" s="1" t="inlineStr">
         <is>
-          <t>2800.00</t>
+          <t>8250.00</t>
         </is>
       </c>
       <c r="AE40" s="1" t="inlineStr">
         <is>
-          <t>2800.00</t>
+          <t>8250.00</t>
         </is>
       </c>
       <c r="AF40" s="1" t="inlineStr">
@@ -9276,7 +9404,7 @@
       </c>
       <c r="AH40" s="1" t="inlineStr">
         <is>
-          <t>Ahorro</t>
+          <t>Crédito Hipotecario</t>
         </is>
       </c>
       <c r="AI40" s="1" t="inlineStr">
@@ -9291,17 +9419,17 @@
       </c>
       <c r="AK40" s="1" t="inlineStr">
         <is>
-          <t>EFECTIVO</t>
+          <t>TRANSFERENCIA BANCARIA</t>
         </is>
       </c>
       <c r="AL40" s="1" t="inlineStr">
         <is>
-          <t>70270427</t>
+          <t>10606793</t>
         </is>
       </c>
       <c r="AM40" s="1" t="inlineStr">
         <is>
-          <t>0500010021</t>
+          <t>02209753</t>
         </is>
       </c>
       <c r="AN40" s="1" t="inlineStr">
@@ -9341,7 +9469,7 @@
       </c>
       <c r="BC40" s="1" t="inlineStr">
         <is>
-          <t>21/06/2025 16:52</t>
+          <t>12/12/2024 16:44</t>
         </is>
       </c>
       <c r="BD40" s="1" t="inlineStr">
@@ -9352,19 +9480,19 @@
       <c r="BE40" s="1" t="inlineStr"/>
       <c r="BF40" s="1" t="inlineStr">
         <is>
-          <t>000002</t>
+          <t>000003</t>
         </is>
       </c>
       <c r="BG40" s="1" t="inlineStr">
         <is>
-          <t>29/05/2026 12:20</t>
+          <t>29/05/2026 12:21</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>RESIDENCIAL BEYOND</t>
+          <t>RESIDENCIAL PRADA</t>
         </is>
       </c>
       <c r="B41" s="1" t="inlineStr">
@@ -9389,17 +9517,17 @@
       </c>
       <c r="F41" s="1" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>701</t>
         </is>
       </c>
       <c r="G41" s="1" t="inlineStr">
         <is>
-          <t>587000.00</t>
+          <t>592500.00</t>
         </is>
       </c>
       <c r="H41" s="1" t="inlineStr">
         <is>
-          <t>577000.00</t>
+          <t>592500.00</t>
         </is>
       </c>
       <c r="I41" s="1" t="inlineStr"/>
@@ -9410,32 +9538,28 @@
       <c r="N41" s="1" t="inlineStr"/>
       <c r="O41" s="1" t="inlineStr">
         <is>
-          <t>Tania Milagros Cotrina Vara</t>
+          <t>Richard Humberto Lima Garcia</t>
         </is>
       </c>
       <c r="P41" s="1" t="inlineStr">
         <is>
-          <t>10140034</t>
+          <t>10606793</t>
         </is>
       </c>
       <c r="Q41" s="1" t="inlineStr">
         <is>
-          <t>Av. Arnaldo Marquez 1526 Dpto. 26</t>
-        </is>
-      </c>
-      <c r="R41" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>Mz E2 lote 10 Urb Coovitiomar - Ancón</t>
+        </is>
+      </c>
+      <c r="R41" s="1" t="inlineStr"/>
       <c r="S41" s="1" t="inlineStr">
         <is>
-          <t>941461159</t>
+          <t>940170759</t>
         </is>
       </c>
       <c r="T41" s="1" t="inlineStr">
         <is>
-          <t>tamicov@hotmail.com</t>
+          <t>richard_13_312@hotmail.com</t>
         </is>
       </c>
       <c r="U41" s="1" t="inlineStr">
@@ -9445,32 +9569,28 @@
       </c>
       <c r="V41" s="1" t="inlineStr">
         <is>
-          <t>JESUS MARIA</t>
+          <t>SANTA ROSA</t>
         </is>
       </c>
       <c r="W41" s="1" t="inlineStr">
         <is>
-          <t>15/12/2024 00:00</t>
-        </is>
-      </c>
-      <c r="X41" s="1" t="inlineStr">
-        <is>
-          <t>15/12/2024 00:00</t>
-        </is>
-      </c>
+          <t>31/12/2024 00:00</t>
+        </is>
+      </c>
+      <c r="X41" s="1" t="inlineStr"/>
       <c r="Y41" s="1" t="inlineStr">
         <is>
-          <t>SEPARACION</t>
+          <t>SALDO FINANCIAR</t>
         </is>
       </c>
       <c r="Z41" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA41" s="1" t="inlineStr">
         <is>
-          <t>3000.00</t>
+          <t>533250.00</t>
         </is>
       </c>
       <c r="AB41" s="1" t="inlineStr">
@@ -9485,72 +9605,40 @@
       </c>
       <c r="AD41" s="1" t="inlineStr">
         <is>
-          <t>3000.00</t>
+          <t>533250.00</t>
         </is>
       </c>
       <c r="AE41" s="1" t="inlineStr">
         <is>
-          <t>3000.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AF41" s="1" t="inlineStr">
         <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="AG41" s="1" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
+          <t>533250.00</t>
+        </is>
+      </c>
+      <c r="AG41" s="1" t="inlineStr"/>
       <c r="AH41" s="1" t="inlineStr">
         <is>
-          <t>Ahorro</t>
-        </is>
-      </c>
-      <c r="AI41" s="1" t="inlineStr">
-        <is>
-          <t>Banco de Credito del Perú</t>
-        </is>
-      </c>
-      <c r="AJ41" s="1" t="inlineStr">
-        <is>
-          <t>194-7325779-0-65</t>
-        </is>
-      </c>
-      <c r="AK41" s="1" t="inlineStr">
-        <is>
-          <t>POS VISA</t>
-        </is>
-      </c>
-      <c r="AL41" s="1" t="inlineStr">
-        <is>
-          <t>10140034</t>
-        </is>
-      </c>
-      <c r="AM41" s="1" t="inlineStr">
-        <is>
-          <t>594693007</t>
-        </is>
-      </c>
+          <t>Crédito Hipotecario</t>
+        </is>
+      </c>
+      <c r="AI41" s="1" t="inlineStr"/>
+      <c r="AJ41" s="1" t="inlineStr"/>
+      <c r="AK41" s="1" t="inlineStr"/>
+      <c r="AL41" s="1" t="inlineStr"/>
+      <c r="AM41" s="1" t="inlineStr"/>
       <c r="AN41" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AO41" s="1" t="inlineStr">
-        <is>
-          <t>NO PRECISA</t>
-        </is>
-      </c>
-      <c r="AP41" s="1" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
+      <c r="AO41" s="1" t="inlineStr"/>
+      <c r="AP41" s="1" t="inlineStr"/>
       <c r="AQ41" s="1" t="inlineStr">
         <is>
-          <t>CANCELADO</t>
+          <t>VENCIDO</t>
         </is>
       </c>
       <c r="AR41" s="1" t="inlineStr"/>
@@ -9565,26 +9653,701 @@
       <c r="BA41" s="1" t="inlineStr"/>
       <c r="BB41" s="1" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>No</t>
         </is>
       </c>
       <c r="BC41" s="1" t="inlineStr">
         <is>
-          <t>18/09/2025 09:59</t>
+          <t>12/12/2024 16:44</t>
         </is>
       </c>
       <c r="BD41" s="1" t="inlineStr">
         <is>
-          <t>Magaly Guevara Perez</t>
+          <t>Carla Michue M</t>
         </is>
       </c>
       <c r="BE41" s="1" t="inlineStr"/>
       <c r="BF41" s="1" t="inlineStr">
         <is>
+          <t>000003</t>
+        </is>
+      </c>
+      <c r="BG41" s="1" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>RESIDENCIAL PRADA</t>
+        </is>
+      </c>
+      <c r="B42" s="1" t="inlineStr">
+        <is>
+          <t>Etapa 1</t>
+        </is>
+      </c>
+      <c r="C42" s="1" t="inlineStr">
+        <is>
+          <t>Edificio</t>
+        </is>
+      </c>
+      <c r="D42" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E42" s="1" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="F42" s="1" t="inlineStr">
+        <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="G42" s="1" t="inlineStr">
+        <is>
+          <t>496000.00</t>
+        </is>
+      </c>
+      <c r="H42" s="1" t="inlineStr">
+        <is>
+          <t>496000.00</t>
+        </is>
+      </c>
+      <c r="I42" s="1" t="inlineStr"/>
+      <c r="J42" s="1" t="inlineStr"/>
+      <c r="K42" s="1" t="inlineStr"/>
+      <c r="L42" s="1" t="inlineStr"/>
+      <c r="M42" s="1" t="inlineStr"/>
+      <c r="N42" s="1" t="inlineStr"/>
+      <c r="O42" s="1" t="inlineStr">
+        <is>
+          <t>Sthefany Carolina Rodriguez Huamán</t>
+        </is>
+      </c>
+      <c r="P42" s="1" t="inlineStr">
+        <is>
+          <t>70270427</t>
+        </is>
+      </c>
+      <c r="Q42" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R42" s="1" t="inlineStr"/>
+      <c r="S42" s="1" t="inlineStr">
+        <is>
+          <t>989492681</t>
+        </is>
+      </c>
+      <c r="T42" s="1" t="inlineStr">
+        <is>
+          <t>sthefany.rodriguez2207@gmail.com</t>
+        </is>
+      </c>
+      <c r="U42" s="1" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="V42" s="1" t="inlineStr">
+        <is>
+          <t>CERCADO DE LIMA</t>
+        </is>
+      </c>
+      <c r="W42" s="1" t="inlineStr">
+        <is>
+          <t>21/10/2024 00:00</t>
+        </is>
+      </c>
+      <c r="X42" s="1" t="inlineStr">
+        <is>
+          <t>21/10/2024 00:00</t>
+        </is>
+      </c>
+      <c r="Y42" s="1" t="inlineStr">
+        <is>
+          <t>SEPARACION</t>
+        </is>
+      </c>
+      <c r="Z42" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA42" s="1" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="AB42" s="1" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AC42" s="1" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AD42" s="1" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="AE42" s="1" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="AF42" s="1" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AG42" s="1" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AH42" s="1" t="inlineStr">
+        <is>
+          <t>Ahorro</t>
+        </is>
+      </c>
+      <c r="AI42" s="1" t="inlineStr">
+        <is>
+          <t>Scotiabank Perú</t>
+        </is>
+      </c>
+      <c r="AJ42" s="1" t="inlineStr">
+        <is>
+          <t>000-2768484</t>
+        </is>
+      </c>
+      <c r="AK42" s="1" t="inlineStr">
+        <is>
+          <t>TRANSFERENCIA BANCARIA</t>
+        </is>
+      </c>
+      <c r="AL42" s="1" t="inlineStr">
+        <is>
+          <t>70270427</t>
+        </is>
+      </c>
+      <c r="AM42" s="1" t="inlineStr">
+        <is>
+          <t>7844655610334</t>
+        </is>
+      </c>
+      <c r="AN42" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AO42" s="1" t="inlineStr">
+        <is>
+          <t>NO PRECISA</t>
+        </is>
+      </c>
+      <c r="AP42" s="1" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="AQ42" s="1" t="inlineStr">
+        <is>
+          <t>CANCELADO</t>
+        </is>
+      </c>
+      <c r="AR42" s="1" t="inlineStr"/>
+      <c r="AS42" s="1" t="inlineStr"/>
+      <c r="AT42" s="1" t="inlineStr"/>
+      <c r="AU42" s="1" t="inlineStr"/>
+      <c r="AV42" s="1" t="inlineStr"/>
+      <c r="AW42" s="1" t="inlineStr"/>
+      <c r="AX42" s="1" t="inlineStr"/>
+      <c r="AY42" s="1" t="inlineStr"/>
+      <c r="AZ42" s="1" t="inlineStr"/>
+      <c r="BA42" s="1" t="inlineStr"/>
+      <c r="BB42" s="1" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="BC42" s="1" t="inlineStr">
+        <is>
+          <t>21/06/2025 16:52</t>
+        </is>
+      </c>
+      <c r="BD42" s="1" t="inlineStr">
+        <is>
+          <t>Carla Michue M</t>
+        </is>
+      </c>
+      <c r="BE42" s="1" t="inlineStr"/>
+      <c r="BF42" s="1" t="inlineStr">
+        <is>
+          <t>000002</t>
+        </is>
+      </c>
+      <c r="BG42" s="1" t="inlineStr">
+        <is>
+          <t>29/05/2026 12:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>RESIDENCIAL PRADA</t>
+        </is>
+      </c>
+      <c r="B43" s="1" t="inlineStr">
+        <is>
+          <t>Etapa 1</t>
+        </is>
+      </c>
+      <c r="C43" s="1" t="inlineStr">
+        <is>
+          <t>Edificio</t>
+        </is>
+      </c>
+      <c r="D43" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E43" s="1" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="F43" s="1" t="inlineStr">
+        <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="G43" s="1" t="inlineStr">
+        <is>
+          <t>496000.00</t>
+        </is>
+      </c>
+      <c r="H43" s="1" t="inlineStr">
+        <is>
+          <t>496000.00</t>
+        </is>
+      </c>
+      <c r="I43" s="1" t="inlineStr"/>
+      <c r="J43" s="1" t="inlineStr"/>
+      <c r="K43" s="1" t="inlineStr"/>
+      <c r="L43" s="1" t="inlineStr"/>
+      <c r="M43" s="1" t="inlineStr"/>
+      <c r="N43" s="1" t="inlineStr"/>
+      <c r="O43" s="1" t="inlineStr">
+        <is>
+          <t>Sthefany Carolina Rodriguez Huamán</t>
+        </is>
+      </c>
+      <c r="P43" s="1" t="inlineStr">
+        <is>
+          <t>70270427</t>
+        </is>
+      </c>
+      <c r="Q43" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R43" s="1" t="inlineStr"/>
+      <c r="S43" s="1" t="inlineStr">
+        <is>
+          <t>989492681</t>
+        </is>
+      </c>
+      <c r="T43" s="1" t="inlineStr">
+        <is>
+          <t>sthefany.rodriguez2207@gmail.com</t>
+        </is>
+      </c>
+      <c r="U43" s="1" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="V43" s="1" t="inlineStr">
+        <is>
+          <t>CERCADO DE LIMA</t>
+        </is>
+      </c>
+      <c r="W43" s="1" t="inlineStr">
+        <is>
+          <t>22/10/2024 00:00</t>
+        </is>
+      </c>
+      <c r="X43" s="1" t="inlineStr">
+        <is>
+          <t>22/10/2024 00:00</t>
+        </is>
+      </c>
+      <c r="Y43" s="1" t="inlineStr">
+        <is>
+          <t>SEPARACION</t>
+        </is>
+      </c>
+      <c r="Z43" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA43" s="1" t="inlineStr">
+        <is>
+          <t>2800.00</t>
+        </is>
+      </c>
+      <c r="AB43" s="1" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AC43" s="1" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AD43" s="1" t="inlineStr">
+        <is>
+          <t>2800.00</t>
+        </is>
+      </c>
+      <c r="AE43" s="1" t="inlineStr">
+        <is>
+          <t>2800.00</t>
+        </is>
+      </c>
+      <c r="AF43" s="1" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AG43" s="1" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AH43" s="1" t="inlineStr">
+        <is>
+          <t>Ahorro</t>
+        </is>
+      </c>
+      <c r="AI43" s="1" t="inlineStr">
+        <is>
+          <t>Scotiabank Perú</t>
+        </is>
+      </c>
+      <c r="AJ43" s="1" t="inlineStr">
+        <is>
+          <t>000-2768484</t>
+        </is>
+      </c>
+      <c r="AK43" s="1" t="inlineStr">
+        <is>
+          <t>EFECTIVO</t>
+        </is>
+      </c>
+      <c r="AL43" s="1" t="inlineStr">
+        <is>
+          <t>70270427</t>
+        </is>
+      </c>
+      <c r="AM43" s="1" t="inlineStr">
+        <is>
+          <t>0500010021</t>
+        </is>
+      </c>
+      <c r="AN43" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AO43" s="1" t="inlineStr">
+        <is>
+          <t>NO PRECISA</t>
+        </is>
+      </c>
+      <c r="AP43" s="1" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="AQ43" s="1" t="inlineStr">
+        <is>
+          <t>CANCELADO</t>
+        </is>
+      </c>
+      <c r="AR43" s="1" t="inlineStr"/>
+      <c r="AS43" s="1" t="inlineStr"/>
+      <c r="AT43" s="1" t="inlineStr"/>
+      <c r="AU43" s="1" t="inlineStr"/>
+      <c r="AV43" s="1" t="inlineStr"/>
+      <c r="AW43" s="1" t="inlineStr"/>
+      <c r="AX43" s="1" t="inlineStr"/>
+      <c r="AY43" s="1" t="inlineStr"/>
+      <c r="AZ43" s="1" t="inlineStr"/>
+      <c r="BA43" s="1" t="inlineStr"/>
+      <c r="BB43" s="1" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="BC43" s="1" t="inlineStr">
+        <is>
+          <t>21/06/2025 16:52</t>
+        </is>
+      </c>
+      <c r="BD43" s="1" t="inlineStr">
+        <is>
+          <t>Carla Michue M</t>
+        </is>
+      </c>
+      <c r="BE43" s="1" t="inlineStr"/>
+      <c r="BF43" s="1" t="inlineStr">
+        <is>
+          <t>000002</t>
+        </is>
+      </c>
+      <c r="BG43" s="1" t="inlineStr">
+        <is>
+          <t>29/05/2026 12:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>RESIDENCIAL BEYOND</t>
+        </is>
+      </c>
+      <c r="B44" s="1" t="inlineStr">
+        <is>
+          <t>Etapa 1</t>
+        </is>
+      </c>
+      <c r="C44" s="1" t="inlineStr">
+        <is>
+          <t>Edificio</t>
+        </is>
+      </c>
+      <c r="D44" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E44" s="1" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="F44" s="1" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="G44" s="1" t="inlineStr">
+        <is>
+          <t>587000.00</t>
+        </is>
+      </c>
+      <c r="H44" s="1" t="inlineStr">
+        <is>
+          <t>577000.00</t>
+        </is>
+      </c>
+      <c r="I44" s="1" t="inlineStr"/>
+      <c r="J44" s="1" t="inlineStr"/>
+      <c r="K44" s="1" t="inlineStr"/>
+      <c r="L44" s="1" t="inlineStr"/>
+      <c r="M44" s="1" t="inlineStr"/>
+      <c r="N44" s="1" t="inlineStr"/>
+      <c r="O44" s="1" t="inlineStr">
+        <is>
+          <t>Tania Milagros Cotrina Vara</t>
+        </is>
+      </c>
+      <c r="P44" s="1" t="inlineStr">
+        <is>
+          <t>10140034</t>
+        </is>
+      </c>
+      <c r="Q44" s="1" t="inlineStr">
+        <is>
+          <t>Av. Arnaldo Marquez 1526 Dpto. 26</t>
+        </is>
+      </c>
+      <c r="R44" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S44" s="1" t="inlineStr">
+        <is>
+          <t>941461159</t>
+        </is>
+      </c>
+      <c r="T44" s="1" t="inlineStr">
+        <is>
+          <t>tamicov@hotmail.com</t>
+        </is>
+      </c>
+      <c r="U44" s="1" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="V44" s="1" t="inlineStr">
+        <is>
+          <t>JESUS MARIA</t>
+        </is>
+      </c>
+      <c r="W44" s="1" t="inlineStr">
+        <is>
+          <t>15/12/2024 00:00</t>
+        </is>
+      </c>
+      <c r="X44" s="1" t="inlineStr">
+        <is>
+          <t>15/12/2024 00:00</t>
+        </is>
+      </c>
+      <c r="Y44" s="1" t="inlineStr">
+        <is>
+          <t>SEPARACION</t>
+        </is>
+      </c>
+      <c r="Z44" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA44" s="1" t="inlineStr">
+        <is>
+          <t>3000.00</t>
+        </is>
+      </c>
+      <c r="AB44" s="1" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AC44" s="1" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AD44" s="1" t="inlineStr">
+        <is>
+          <t>3000.00</t>
+        </is>
+      </c>
+      <c r="AE44" s="1" t="inlineStr">
+        <is>
+          <t>3000.00</t>
+        </is>
+      </c>
+      <c r="AF44" s="1" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AG44" s="1" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AH44" s="1" t="inlineStr">
+        <is>
+          <t>Ahorro</t>
+        </is>
+      </c>
+      <c r="AI44" s="1" t="inlineStr">
+        <is>
+          <t>Banco de Credito del Perú</t>
+        </is>
+      </c>
+      <c r="AJ44" s="1" t="inlineStr">
+        <is>
+          <t>194-7325779-0-65</t>
+        </is>
+      </c>
+      <c r="AK44" s="1" t="inlineStr">
+        <is>
+          <t>POS VISA</t>
+        </is>
+      </c>
+      <c r="AL44" s="1" t="inlineStr">
+        <is>
+          <t>10140034</t>
+        </is>
+      </c>
+      <c r="AM44" s="1" t="inlineStr">
+        <is>
+          <t>594693007</t>
+        </is>
+      </c>
+      <c r="AN44" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AO44" s="1" t="inlineStr">
+        <is>
+          <t>NO PRECISA</t>
+        </is>
+      </c>
+      <c r="AP44" s="1" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="AQ44" s="1" t="inlineStr">
+        <is>
+          <t>CANCELADO</t>
+        </is>
+      </c>
+      <c r="AR44" s="1" t="inlineStr"/>
+      <c r="AS44" s="1" t="inlineStr"/>
+      <c r="AT44" s="1" t="inlineStr"/>
+      <c r="AU44" s="1" t="inlineStr"/>
+      <c r="AV44" s="1" t="inlineStr"/>
+      <c r="AW44" s="1" t="inlineStr"/>
+      <c r="AX44" s="1" t="inlineStr"/>
+      <c r="AY44" s="1" t="inlineStr"/>
+      <c r="AZ44" s="1" t="inlineStr"/>
+      <c r="BA44" s="1" t="inlineStr"/>
+      <c r="BB44" s="1" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="BC44" s="1" t="inlineStr">
+        <is>
+          <t>18/09/2025 09:59</t>
+        </is>
+      </c>
+      <c r="BD44" s="1" t="inlineStr">
+        <is>
+          <t>Magaly Guevara Perez</t>
+        </is>
+      </c>
+      <c r="BE44" s="1" t="inlineStr"/>
+      <c r="BF44" s="1" t="inlineStr">
+        <is>
           <t>000004</t>
         </is>
       </c>
-      <c r="BG41" s="1" t="inlineStr">
+      <c r="BG44" s="1" t="inlineStr">
         <is>
           <t>01/05/2026 11:00</t>
         </is>
